--- a/research/traditional_assets/database/data/sweden/sweden_software_internet.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_software_internet.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1656,22 +1656,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1005705269765737</v>
+        <v>0.100399081691002</v>
       </c>
       <c r="C2">
-        <v>77.44030911146442</v>
+        <v>76.85694141198215</v>
       </c>
       <c r="D2">
-        <v>75.04030911146441</v>
+        <v>75.27594141198215</v>
       </c>
       <c r="E2">
-        <v>-19.1</v>
+        <v>-18.281</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8190000000000001</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -1692,28 +1692,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0411957</v>
       </c>
       <c r="N2">
-        <v>5.663061224489796</v>
+        <v>5.621865524489796</v>
       </c>
       <c r="O2">
-        <v>1.166590612244898</v>
+        <v>1.158104298044898</v>
       </c>
       <c r="P2">
-        <v>4.496470612244899</v>
+        <v>4.463761226444898</v>
       </c>
       <c r="Q2">
-        <v>7.486470612244899</v>
+        <v>7.453761226444898</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1005705269765737</v>
+        <v>0.1010097976676788</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.275053063918678</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>137.467289656197</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.100399081691002</v>
+        <v>0.1002276364054302</v>
       </c>
       <c r="C3">
-        <v>76.85694141198215</v>
+        <v>76.27505818067527</v>
       </c>
       <c r="D3">
-        <v>75.27594141198215</v>
+        <v>75.51305818067527</v>
       </c>
       <c r="E3">
-        <v>-18.281</v>
+        <v>-17.462</v>
       </c>
       <c r="F3">
-        <v>0.8190000000000001</v>
+        <v>1.638</v>
       </c>
       <c r="G3">
         <v>2.4</v>
@@ -1774,28 +1774,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M3">
-        <v>0.0411957</v>
+        <v>0.0823914</v>
       </c>
       <c r="N3">
-        <v>5.621865524489796</v>
+        <v>5.580669824489797</v>
       </c>
       <c r="O3">
-        <v>1.158104298044898</v>
+        <v>1.149617983844898</v>
       </c>
       <c r="P3">
-        <v>4.463761226444898</v>
+        <v>4.431051840644899</v>
       </c>
       <c r="Q3">
-        <v>7.453761226444898</v>
+        <v>7.421051840644899</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1010097976676788</v>
+        <v>0.1014580330667655</v>
       </c>
       <c r="T3">
-        <v>1.275053063918678</v>
+        <v>1.28540492071052</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>137.467289656197</v>
+        <v>68.73364482809852</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1002276364054302</v>
+        <v>0.1000561911198585</v>
       </c>
       <c r="C4">
-        <v>76.27505818067527</v>
+        <v>75.69467348995089</v>
       </c>
       <c r="D4">
-        <v>75.51305818067527</v>
+        <v>75.75167348995087</v>
       </c>
       <c r="E4">
-        <v>-17.462</v>
+        <v>-16.643</v>
       </c>
       <c r="F4">
-        <v>1.638</v>
+        <v>2.457</v>
       </c>
       <c r="G4">
         <v>2.4</v>
@@ -1856,28 +1856,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M4">
-        <v>0.0823914</v>
+        <v>0.1235871</v>
       </c>
       <c r="N4">
-        <v>5.580669824489797</v>
+        <v>5.539474124489796</v>
       </c>
       <c r="O4">
-        <v>1.149617983844898</v>
+        <v>1.141131669644898</v>
       </c>
       <c r="P4">
-        <v>4.431051840644899</v>
+        <v>4.398342454844898</v>
       </c>
       <c r="Q4">
-        <v>7.421051840644899</v>
+        <v>7.388342454844898</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1014580330667655</v>
+        <v>0.1019155104328438</v>
       </c>
       <c r="T4">
-        <v>1.28540492071052</v>
+        <v>1.295970217848587</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>68.73364482809852</v>
+        <v>45.82242988539901</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1000561911198585</v>
+        <v>0.09988474583428675</v>
       </c>
       <c r="C5">
-        <v>75.69467348995089</v>
+        <v>75.11580159065073</v>
       </c>
       <c r="D5">
-        <v>75.75167348995087</v>
+        <v>75.99180159065072</v>
       </c>
       <c r="E5">
-        <v>-16.643</v>
+        <v>-15.824</v>
       </c>
       <c r="F5">
-        <v>2.457</v>
+        <v>3.276</v>
       </c>
       <c r="G5">
         <v>2.4</v>
@@ -1938,28 +1938,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M5">
-        <v>0.1235871</v>
+        <v>0.1647828</v>
       </c>
       <c r="N5">
-        <v>5.539474124489796</v>
+        <v>5.498278424489796</v>
       </c>
       <c r="O5">
-        <v>1.141131669644898</v>
+        <v>1.132645355444898</v>
       </c>
       <c r="P5">
-        <v>4.398342454844898</v>
+        <v>4.365633069044899</v>
       </c>
       <c r="Q5">
-        <v>7.388342454844898</v>
+        <v>7.355633069044899</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1019155104328438</v>
+        <v>0.102382518577382</v>
       </c>
       <c r="T5">
-        <v>1.295970217848587</v>
+        <v>1.306755625343696</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.82242988539901</v>
+        <v>34.36682241404926</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09988474583428675</v>
+        <v>0.09971330054871501</v>
       </c>
       <c r="C6">
-        <v>75.11580159065073</v>
+        <v>74.53845691488836</v>
       </c>
       <c r="D6">
-        <v>75.99180159065072</v>
+        <v>76.23345691488835</v>
       </c>
       <c r="E6">
-        <v>-15.824</v>
+        <v>-15.005</v>
       </c>
       <c r="F6">
-        <v>3.276</v>
+        <v>4.095000000000001</v>
       </c>
       <c r="G6">
         <v>2.4</v>
@@ -2020,28 +2020,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M6">
-        <v>0.1647828</v>
+        <v>0.2059785</v>
       </c>
       <c r="N6">
-        <v>5.498278424489796</v>
+        <v>5.457082724489797</v>
       </c>
       <c r="O6">
-        <v>1.132645355444898</v>
+        <v>1.124159041244898</v>
       </c>
       <c r="P6">
-        <v>4.365633069044899</v>
+        <v>4.332923683244898</v>
       </c>
       <c r="Q6">
-        <v>7.355633069044899</v>
+        <v>7.322923683244898</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.102382518577382</v>
+        <v>0.1028593584723316</v>
       </c>
       <c r="T6">
-        <v>1.306755625343696</v>
+        <v>1.317768094049228</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.36682241404926</v>
+        <v>27.49345793123941</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09971330054871501</v>
+        <v>0.09954185526314326</v>
       </c>
       <c r="C7">
-        <v>74.53845691488836</v>
+        <v>73.96265407894046</v>
       </c>
       <c r="D7">
-        <v>76.23345691488835</v>
+        <v>76.47665407894046</v>
       </c>
       <c r="E7">
-        <v>-15.005</v>
+        <v>-14.186</v>
       </c>
       <c r="F7">
-        <v>4.095000000000001</v>
+        <v>4.914000000000001</v>
       </c>
       <c r="G7">
         <v>2.4</v>
@@ -2102,28 +2102,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M7">
-        <v>0.2059785</v>
+        <v>0.2471742</v>
       </c>
       <c r="N7">
-        <v>5.457082724489797</v>
+        <v>5.415887024489797</v>
       </c>
       <c r="O7">
-        <v>1.124159041244898</v>
+        <v>1.115672727044898</v>
       </c>
       <c r="P7">
-        <v>4.332923683244898</v>
+        <v>4.300214297444898</v>
       </c>
       <c r="Q7">
-        <v>7.322923683244898</v>
+        <v>7.290214297444899</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1028593584723316</v>
+        <v>0.1033463438969609</v>
       </c>
       <c r="T7">
-        <v>1.317768094049228</v>
+        <v>1.329014870599559</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.49345793123941</v>
+        <v>22.91121494269951</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2148,22 +2148,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09954185526314326</v>
+        <v>0.09937040997757153</v>
       </c>
       <c r="C8">
-        <v>73.96265407894046</v>
+        <v>73.38840788619382</v>
       </c>
       <c r="D8">
-        <v>76.47665407894046</v>
+        <v>76.72140788619382</v>
       </c>
       <c r="E8">
-        <v>-14.186</v>
+        <v>-13.367</v>
       </c>
       <c r="F8">
-        <v>4.914000000000001</v>
+        <v>5.733</v>
       </c>
       <c r="G8">
         <v>2.4</v>
@@ -2184,28 +2184,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M8">
-        <v>0.2471742</v>
+        <v>0.2883699</v>
       </c>
       <c r="N8">
-        <v>5.415887024489797</v>
+        <v>5.374691324489796</v>
       </c>
       <c r="O8">
-        <v>1.115672727044898</v>
+        <v>1.107186412844898</v>
       </c>
       <c r="P8">
-        <v>4.300214297444898</v>
+        <v>4.267504911644898</v>
       </c>
       <c r="Q8">
-        <v>7.290214297444899</v>
+        <v>7.257504911644898</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1033463438969609</v>
+        <v>0.103843802126421</v>
       </c>
       <c r="T8">
-        <v>1.329014870599559</v>
+        <v>1.340503513312263</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.91121494269951</v>
+        <v>19.63818423659958</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2230,22 +2230,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09937040997757152</v>
+        <v>0.09919896469199978</v>
       </c>
       <c r="C9">
-        <v>73.38840788619383</v>
+        <v>72.81573333014921</v>
       </c>
       <c r="D9">
-        <v>76.72140788619383</v>
+        <v>76.96773333014922</v>
       </c>
       <c r="E9">
-        <v>-13.367</v>
+        <v>-12.548</v>
       </c>
       <c r="F9">
-        <v>5.733000000000001</v>
+        <v>6.552</v>
       </c>
       <c r="G9">
         <v>2.4</v>
@@ -2266,28 +2266,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M9">
-        <v>0.2883699</v>
+        <v>0.3295656</v>
       </c>
       <c r="N9">
-        <v>5.374691324489796</v>
+        <v>5.333495624489796</v>
       </c>
       <c r="O9">
-        <v>1.107186412844898</v>
+        <v>1.098700098644898</v>
       </c>
       <c r="P9">
-        <v>4.267504911644898</v>
+        <v>4.234795525844898</v>
       </c>
       <c r="Q9">
-        <v>7.257504911644898</v>
+        <v>7.224795525844899</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.103843802126421</v>
+        <v>0.1043520746652171</v>
       </c>
       <c r="T9">
-        <v>1.340503513312263</v>
+        <v>1.352241909127417</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.63818423659957</v>
+        <v>17.18341120702463</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09919896469199978</v>
+        <v>0.09902751940642804</v>
       </c>
       <c r="C10">
-        <v>72.81573333014921</v>
+        <v>72.24464559748294</v>
       </c>
       <c r="D10">
-        <v>76.96773333014922</v>
+        <v>77.21564559748293</v>
       </c>
       <c r="E10">
-        <v>-12.548</v>
+        <v>-11.729</v>
       </c>
       <c r="F10">
-        <v>6.552</v>
+        <v>7.371</v>
       </c>
       <c r="G10">
         <v>2.4</v>
@@ -2348,28 +2348,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M10">
-        <v>0.3295656</v>
+        <v>0.3707613</v>
       </c>
       <c r="N10">
-        <v>5.333495624489796</v>
+        <v>5.292299924489797</v>
       </c>
       <c r="O10">
-        <v>1.098700098644898</v>
+        <v>1.090213784444898</v>
       </c>
       <c r="P10">
-        <v>4.234795525844898</v>
+        <v>4.202086140044898</v>
       </c>
       <c r="Q10">
-        <v>7.224795525844899</v>
+        <v>7.192086140044898</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1043520746652171</v>
+        <v>0.1048715180290418</v>
       </c>
       <c r="T10">
-        <v>1.352241909127417</v>
+        <v>1.364238291663783</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.18341120702463</v>
+        <v>15.274143295133</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2394,22 +2394,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09902751940642804</v>
+        <v>0.09885607412085629</v>
       </c>
       <c r="C11">
-        <v>72.24464559748294</v>
+        <v>71.67516007116812</v>
       </c>
       <c r="D11">
-        <v>77.21564559748293</v>
+        <v>77.46516007116811</v>
       </c>
       <c r="E11">
-        <v>-11.729</v>
+        <v>-10.91</v>
       </c>
       <c r="F11">
-        <v>7.371</v>
+        <v>8.19</v>
       </c>
       <c r="G11">
         <v>2.4</v>
@@ -2430,28 +2430,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M11">
-        <v>0.3707613</v>
+        <v>0.411957</v>
       </c>
       <c r="N11">
-        <v>5.292299924489797</v>
+        <v>5.251104224489796</v>
       </c>
       <c r="O11">
-        <v>1.090213784444898</v>
+        <v>1.081727470244898</v>
       </c>
       <c r="P11">
-        <v>4.202086140044898</v>
+        <v>4.169376754244898</v>
       </c>
       <c r="Q11">
-        <v>7.192086140044898</v>
+        <v>7.159376754244898</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1048715180290418</v>
+        <v>0.1054025045787292</v>
       </c>
       <c r="T11">
-        <v>1.364238291663783</v>
+        <v>1.376501260478735</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.274143295133</v>
+        <v>13.7467289656197</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2476,22 +2476,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09885607412085629</v>
+        <v>0.09881563883528456</v>
       </c>
       <c r="C12">
-        <v>71.67516007116812</v>
+        <v>70.91524312549232</v>
       </c>
       <c r="D12">
-        <v>77.46516007116811</v>
+        <v>77.52424312549232</v>
       </c>
       <c r="E12">
-        <v>-10.91</v>
+        <v>-10.091</v>
       </c>
       <c r="F12">
-        <v>8.190000000000001</v>
+        <v>9.009</v>
       </c>
       <c r="G12">
         <v>2.4</v>
@@ -2512,45 +2512,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M12">
-        <v>0.411957</v>
+        <v>0.4666662</v>
       </c>
       <c r="N12">
-        <v>5.251104224489796</v>
+        <v>5.196395024489797</v>
       </c>
       <c r="O12">
-        <v>1.081727470244898</v>
+        <v>1.070457375044898</v>
       </c>
       <c r="P12">
-        <v>4.169376754244898</v>
+        <v>4.125937649444898</v>
       </c>
       <c r="Q12">
-        <v>7.159376754244898</v>
+        <v>7.115937649444898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1054025045787292</v>
+        <v>0.1059454234104321</v>
       </c>
       <c r="T12">
-        <v>1.376501260478735</v>
+        <v>1.389039801626607</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.206</v>
       </c>
       <c r="W12">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.7467289656197</v>
+        <v>12.13514333047861</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2558,22 +2558,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09881563883528456</v>
+        <v>0.09865610354971281</v>
       </c>
       <c r="C13">
-        <v>70.91524312549232</v>
+        <v>70.3302341205744</v>
       </c>
       <c r="D13">
-        <v>77.52424312549232</v>
+        <v>77.7582341205744</v>
       </c>
       <c r="E13">
-        <v>-10.091</v>
+        <v>-9.272</v>
       </c>
       <c r="F13">
-        <v>9.009</v>
+        <v>9.828000000000001</v>
       </c>
       <c r="G13">
         <v>2.4</v>
@@ -2594,28 +2594,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M13">
-        <v>0.4666662</v>
+        <v>0.5090904000000001</v>
       </c>
       <c r="N13">
-        <v>5.196395024489797</v>
+        <v>5.153970824489797</v>
       </c>
       <c r="O13">
-        <v>1.070457375044898</v>
+        <v>1.061717989844898</v>
       </c>
       <c r="P13">
-        <v>4.125937649444898</v>
+        <v>4.092252834644898</v>
       </c>
       <c r="Q13">
-        <v>7.115937649444898</v>
+        <v>7.082252834644899</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1059454234104321</v>
+        <v>0.1065006813064918</v>
       </c>
       <c r="T13">
-        <v>1.389039801626607</v>
+        <v>1.401863309618749</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.13514333047861</v>
+        <v>11.12388138627206</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2640,22 +2640,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09865610354971281</v>
+        <v>0.09849656826414108</v>
       </c>
       <c r="C14">
-        <v>70.3302341205744</v>
+        <v>69.74664189938456</v>
       </c>
       <c r="D14">
-        <v>77.7582341205744</v>
+        <v>77.99364189938456</v>
       </c>
       <c r="E14">
-        <v>-9.272</v>
+        <v>-8.453000000000001</v>
       </c>
       <c r="F14">
-        <v>9.828000000000001</v>
+        <v>10.647</v>
       </c>
       <c r="G14">
         <v>2.4</v>
@@ -2676,28 +2676,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M14">
-        <v>0.5090904000000001</v>
+        <v>0.5515146</v>
       </c>
       <c r="N14">
-        <v>5.153970824489797</v>
+        <v>5.111546624489796</v>
       </c>
       <c r="O14">
-        <v>1.061717989844898</v>
+        <v>1.052978604644898</v>
       </c>
       <c r="P14">
-        <v>4.092252834644898</v>
+        <v>4.058568019844898</v>
       </c>
       <c r="Q14">
-        <v>7.082252834644899</v>
+        <v>7.048568019844899</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1065006813064918</v>
+        <v>0.1070687037518863</v>
       </c>
       <c r="T14">
-        <v>1.401863309618749</v>
+        <v>1.414981610898067</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.12388138627206</v>
+        <v>10.26819820271267</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09849656826414108</v>
+        <v>0.09852600497856932</v>
       </c>
       <c r="C15">
-        <v>69.74664189938456</v>
+        <v>68.88409836589014</v>
       </c>
       <c r="D15">
-        <v>77.99364189938456</v>
+        <v>77.95009836589014</v>
       </c>
       <c r="E15">
-        <v>-8.453000000000001</v>
+        <v>-7.634</v>
       </c>
       <c r="F15">
-        <v>10.647</v>
+        <v>11.466</v>
       </c>
       <c r="G15">
         <v>2.4</v>
@@ -2758,45 +2758,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M15">
-        <v>0.5515146</v>
+        <v>0.6134310000000001</v>
       </c>
       <c r="N15">
-        <v>5.111546624489796</v>
+        <v>5.049630224489796</v>
       </c>
       <c r="O15">
-        <v>1.052978604644898</v>
+        <v>1.040223826244898</v>
       </c>
       <c r="P15">
-        <v>4.058568019844898</v>
+        <v>4.009406398244898</v>
       </c>
       <c r="Q15">
-        <v>7.048568019844899</v>
+        <v>6.999406398244898</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1070687037518863</v>
+        <v>0.1076499360215922</v>
       </c>
       <c r="T15">
-        <v>1.414981610898067</v>
+        <v>1.428404988951322</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.206</v>
       </c>
       <c r="W15">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.26819820271267</v>
+        <v>9.231781935522978</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2804,22 +2804,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09852600497856932</v>
+        <v>0.09837996769299759</v>
       </c>
       <c r="C16">
-        <v>68.88409836589014</v>
+        <v>68.28159946459509</v>
       </c>
       <c r="D16">
-        <v>77.95009836589014</v>
+        <v>78.16659946459508</v>
       </c>
       <c r="E16">
-        <v>-7.634</v>
+        <v>-6.815</v>
       </c>
       <c r="F16">
-        <v>11.466</v>
+        <v>12.285</v>
       </c>
       <c r="G16">
         <v>2.4</v>
@@ -2840,28 +2840,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M16">
-        <v>0.6134310000000001</v>
+        <v>0.6572475000000001</v>
       </c>
       <c r="N16">
-        <v>5.049630224489796</v>
+        <v>5.005813724489796</v>
       </c>
       <c r="O16">
-        <v>1.040223826244898</v>
+        <v>1.031197627244898</v>
       </c>
       <c r="P16">
-        <v>4.009406398244898</v>
+        <v>3.974616097244898</v>
       </c>
       <c r="Q16">
-        <v>6.999406398244898</v>
+        <v>6.964616097244898</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1076499360215922</v>
+        <v>0.1082448443447031</v>
       </c>
       <c r="T16">
-        <v>1.428404988951322</v>
+        <v>1.442144211194066</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.231781935522978</v>
+        <v>8.616329806488112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2886,22 +2886,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09837996769299759</v>
+        <v>0.09823393040742584</v>
       </c>
       <c r="C17">
-        <v>68.28159946459509</v>
+        <v>67.68030654700307</v>
       </c>
       <c r="D17">
-        <v>78.16659946459508</v>
+        <v>78.38430654700306</v>
       </c>
       <c r="E17">
-        <v>-6.815000000000001</v>
+        <v>-5.996</v>
       </c>
       <c r="F17">
-        <v>12.285</v>
+        <v>13.104</v>
       </c>
       <c r="G17">
         <v>2.4</v>
@@ -2922,28 +2922,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M17">
-        <v>0.6572475</v>
+        <v>0.701064</v>
       </c>
       <c r="N17">
-        <v>5.005813724489796</v>
+        <v>4.961997224489797</v>
       </c>
       <c r="O17">
-        <v>1.031197627244898</v>
+        <v>1.022171428244898</v>
       </c>
       <c r="P17">
-        <v>3.974616097244898</v>
+        <v>3.939825796244898</v>
       </c>
       <c r="Q17">
-        <v>6.964616097244898</v>
+        <v>6.929825796244899</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1082448443447031</v>
+        <v>0.1088539171516974</v>
       </c>
       <c r="T17">
-        <v>1.442144211194066</v>
+        <v>1.456210557775922</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.616329806488114</v>
+        <v>8.077809193582606</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2968,22 +2968,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09823393040742584</v>
+        <v>0.09819587712185411</v>
       </c>
       <c r="C18">
-        <v>67.68030654700307</v>
+        <v>66.91823431623266</v>
       </c>
       <c r="D18">
-        <v>78.38430654700306</v>
+        <v>78.44123431623265</v>
       </c>
       <c r="E18">
-        <v>-5.996</v>
+        <v>-5.177</v>
       </c>
       <c r="F18">
-        <v>13.104</v>
+        <v>13.923</v>
       </c>
       <c r="G18">
         <v>2.4</v>
@@ -3004,45 +3004,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M18">
-        <v>0.701064</v>
+        <v>0.7560189000000002</v>
       </c>
       <c r="N18">
-        <v>4.961997224489797</v>
+        <v>4.907042324489796</v>
       </c>
       <c r="O18">
-        <v>1.022171428244898</v>
+        <v>1.010850718844898</v>
       </c>
       <c r="P18">
-        <v>3.939825796244898</v>
+        <v>3.896191605644899</v>
       </c>
       <c r="Q18">
-        <v>6.929825796244899</v>
+        <v>6.886191605644899</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1088539171516974</v>
+        <v>0.1094776664118724</v>
       </c>
       <c r="T18">
-        <v>1.456210557775922</v>
+        <v>1.470615852468185</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.077809193582606</v>
+        <v>7.490634459654111</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3050,22 +3050,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09819587712185411</v>
+        <v>0.09805619183628236</v>
       </c>
       <c r="C19">
-        <v>66.91823431623266</v>
+        <v>66.30891446763732</v>
       </c>
       <c r="D19">
-        <v>78.44123431623265</v>
+        <v>78.65091446763732</v>
       </c>
       <c r="E19">
-        <v>-5.177</v>
+        <v>-4.357999999999999</v>
       </c>
       <c r="F19">
-        <v>13.923</v>
+        <v>14.742</v>
       </c>
       <c r="G19">
         <v>2.4</v>
@@ -3086,28 +3086,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M19">
-        <v>0.7560189000000002</v>
+        <v>0.8004906000000002</v>
       </c>
       <c r="N19">
-        <v>4.907042324489796</v>
+        <v>4.862570624489797</v>
       </c>
       <c r="O19">
-        <v>1.010850718844898</v>
+        <v>1.001689548644898</v>
       </c>
       <c r="P19">
-        <v>3.896191605644899</v>
+        <v>3.860881075844898</v>
       </c>
       <c r="Q19">
-        <v>6.886191605644899</v>
+        <v>6.850881075844899</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1094776664118724</v>
+        <v>0.110116629068637</v>
       </c>
       <c r="T19">
-        <v>1.470615852468185</v>
+        <v>1.485372495811479</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.490634459654111</v>
+        <v>7.074488100784438</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3132,22 +3132,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09805619183628238</v>
+        <v>0.09791650655071062</v>
       </c>
       <c r="C20">
-        <v>66.30891446763731</v>
+        <v>65.70071860964559</v>
       </c>
       <c r="D20">
-        <v>78.65091446763731</v>
+        <v>78.86171860964559</v>
       </c>
       <c r="E20">
-        <v>-4.358000000000001</v>
+        <v>-3.539</v>
       </c>
       <c r="F20">
-        <v>14.742</v>
+        <v>15.561</v>
       </c>
       <c r="G20">
         <v>2.4</v>
@@ -3168,28 +3168,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M20">
-        <v>0.8004906000000001</v>
+        <v>0.8449623000000001</v>
       </c>
       <c r="N20">
-        <v>4.862570624489797</v>
+        <v>4.818098924489797</v>
       </c>
       <c r="O20">
-        <v>1.001689548644898</v>
+        <v>0.9925283784448982</v>
       </c>
       <c r="P20">
-        <v>3.860881075844898</v>
+        <v>3.825570546044899</v>
       </c>
       <c r="Q20">
-        <v>6.850881075844899</v>
+        <v>6.815570546044899</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.110116629068637</v>
+        <v>0.1107713685811242</v>
       </c>
       <c r="T20">
-        <v>1.485372495811479</v>
+        <v>1.500493500718804</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.074488100784439</v>
+        <v>6.702146621795785</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3214,22 +3214,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09791650655071062</v>
+        <v>0.09777682126513891</v>
       </c>
       <c r="C21">
-        <v>65.70071860964559</v>
+        <v>65.09365580427456</v>
       </c>
       <c r="D21">
-        <v>78.86171860964559</v>
+        <v>79.07365580427455</v>
       </c>
       <c r="E21">
-        <v>-3.539</v>
+        <v>-2.719999999999999</v>
       </c>
       <c r="F21">
-        <v>15.561</v>
+        <v>16.38</v>
       </c>
       <c r="G21">
         <v>2.4</v>
@@ -3250,28 +3250,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M21">
-        <v>0.8449623000000001</v>
+        <v>0.8894340000000002</v>
       </c>
       <c r="N21">
-        <v>4.818098924489797</v>
+        <v>4.773627224489796</v>
       </c>
       <c r="O21">
-        <v>0.9925283784448982</v>
+        <v>0.9833672082448981</v>
       </c>
       <c r="P21">
-        <v>3.825570546044899</v>
+        <v>3.790260016244898</v>
       </c>
       <c r="Q21">
-        <v>6.815570546044899</v>
+        <v>6.780260016244898</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1107713685811242</v>
+        <v>0.1114424765814236</v>
       </c>
       <c r="T21">
-        <v>1.500493500718804</v>
+        <v>1.515992530748813</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.702146621795785</v>
+        <v>6.367039290705994</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3296,22 +3296,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09777682126513891</v>
+        <v>0.09780387597956715</v>
       </c>
       <c r="C22">
-        <v>65.09365580427456</v>
+        <v>64.23351819411984</v>
       </c>
       <c r="D22">
-        <v>79.07365580427455</v>
+        <v>79.03251819411983</v>
       </c>
       <c r="E22">
-        <v>-2.719999999999999</v>
+        <v>-1.901</v>
       </c>
       <c r="F22">
-        <v>16.38</v>
+        <v>17.199</v>
       </c>
       <c r="G22">
         <v>2.4</v>
@@ -3332,45 +3332,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M22">
-        <v>0.8894340000000002</v>
+        <v>0.9511047000000001</v>
       </c>
       <c r="N22">
-        <v>4.773627224489796</v>
+        <v>4.711956524489796</v>
       </c>
       <c r="O22">
-        <v>0.9833672082448981</v>
+        <v>0.9706630440448981</v>
       </c>
       <c r="P22">
-        <v>3.790260016244898</v>
+        <v>3.741293480444898</v>
       </c>
       <c r="Q22">
-        <v>6.780260016244898</v>
+        <v>6.731293480444899</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1114424765814236</v>
+        <v>0.1121305746576799</v>
       </c>
       <c r="T22">
-        <v>1.515992530748813</v>
+        <v>1.53188394128591</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.367039290705994</v>
+        <v>5.954193291747791</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3378,22 +3378,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09780387597956715</v>
+        <v>0.09767213069399538</v>
       </c>
       <c r="C23">
-        <v>64.23351819411984</v>
+        <v>63.61524566645684</v>
       </c>
       <c r="D23">
-        <v>79.03251819411983</v>
+        <v>79.23324566645684</v>
       </c>
       <c r="E23">
-        <v>-1.901</v>
+        <v>-1.082000000000001</v>
       </c>
       <c r="F23">
-        <v>17.199</v>
+        <v>18.018</v>
       </c>
       <c r="G23">
         <v>2.4</v>
@@ -3414,28 +3414,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M23">
-        <v>0.9511047000000001</v>
+        <v>0.9963954</v>
       </c>
       <c r="N23">
-        <v>4.711956524489796</v>
+        <v>4.666665824489796</v>
       </c>
       <c r="O23">
-        <v>0.9706630440448981</v>
+        <v>0.9613331598448982</v>
       </c>
       <c r="P23">
-        <v>3.741293480444898</v>
+        <v>3.705332664644899</v>
       </c>
       <c r="Q23">
-        <v>6.731293480444899</v>
+        <v>6.695332664644899</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1121305746576799</v>
+        <v>0.1128363162743531</v>
       </c>
       <c r="T23">
-        <v>1.53188394128591</v>
+        <v>1.548182823888061</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.954193291747791</v>
+        <v>5.683548142122892</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3460,22 +3460,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09767213069399538</v>
+        <v>0.09754038540842366</v>
       </c>
       <c r="C24">
-        <v>63.61524566645684</v>
+        <v>62.99799535376013</v>
       </c>
       <c r="D24">
-        <v>79.23324566645684</v>
+        <v>79.43499535376013</v>
       </c>
       <c r="E24">
-        <v>-1.082000000000001</v>
+        <v>-0.2629999999999981</v>
       </c>
       <c r="F24">
-        <v>18.018</v>
+        <v>18.837</v>
       </c>
       <c r="G24">
         <v>2.4</v>
@@ -3496,28 +3496,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M24">
-        <v>0.9963954</v>
+        <v>1.0416861</v>
       </c>
       <c r="N24">
-        <v>4.666665824489796</v>
+        <v>4.621375124489797</v>
       </c>
       <c r="O24">
-        <v>0.9613331598448982</v>
+        <v>0.9520032756448982</v>
       </c>
       <c r="P24">
-        <v>3.705332664644899</v>
+        <v>3.669371848844898</v>
       </c>
       <c r="Q24">
-        <v>6.695332664644899</v>
+        <v>6.659371848844899</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1128363162743531</v>
+        <v>0.1135603888421086</v>
       </c>
       <c r="T24">
-        <v>1.548182823888061</v>
+        <v>1.564905054090269</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.683548142122892</v>
+        <v>5.436437353334941</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09754038540842366</v>
+        <v>0.09740864012285191</v>
       </c>
       <c r="C25">
-        <v>62.99799535376013</v>
+        <v>62.38177508448661</v>
       </c>
       <c r="D25">
-        <v>79.43499535376013</v>
+        <v>79.63777508448661</v>
       </c>
       <c r="E25">
-        <v>-0.2629999999999981</v>
+        <v>0.5560000000000009</v>
       </c>
       <c r="F25">
-        <v>18.837</v>
+        <v>19.656</v>
       </c>
       <c r="G25">
         <v>2.4</v>
@@ -3578,28 +3578,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M25">
-        <v>1.0416861</v>
+        <v>1.0869768</v>
       </c>
       <c r="N25">
-        <v>4.621375124489797</v>
+        <v>4.576084424489796</v>
       </c>
       <c r="O25">
-        <v>0.9520032756448982</v>
+        <v>0.942673391444898</v>
       </c>
       <c r="P25">
-        <v>3.669371848844898</v>
+        <v>3.633411033044898</v>
       </c>
       <c r="Q25">
-        <v>6.659371848844899</v>
+        <v>6.623411033044898</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1135603888421086</v>
+        <v>0.1143035159511209</v>
       </c>
       <c r="T25">
-        <v>1.564905054090269</v>
+        <v>1.582067342982008</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.436437353334941</v>
+        <v>5.209919130279317</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0974086401228519</v>
+        <v>0.09727689483728018</v>
       </c>
       <c r="C26">
-        <v>62.38177508448663</v>
+        <v>61.76659276723473</v>
       </c>
       <c r="D26">
-        <v>79.63777508448663</v>
+        <v>79.84159276723473</v>
       </c>
       <c r="E26">
-        <v>0.5560000000000009</v>
+        <v>1.375</v>
       </c>
       <c r="F26">
-        <v>19.656</v>
+        <v>20.475</v>
       </c>
       <c r="G26">
         <v>2.4</v>
@@ -3660,28 +3660,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M26">
-        <v>1.0869768</v>
+        <v>1.1322675</v>
       </c>
       <c r="N26">
-        <v>4.576084424489796</v>
+        <v>4.530793724489796</v>
       </c>
       <c r="O26">
-        <v>0.942673391444898</v>
+        <v>0.9333435072448981</v>
       </c>
       <c r="P26">
-        <v>3.633411033044898</v>
+        <v>3.597450217244898</v>
       </c>
       <c r="Q26">
-        <v>6.623411033044898</v>
+        <v>6.587450217244898</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1143035159511209</v>
+        <v>0.1150664597830402</v>
       </c>
       <c r="T26">
-        <v>1.582067342982008</v>
+        <v>1.59968729291086</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.209919130279317</v>
+        <v>5.001522365068144</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3706,22 +3706,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09727689483728018</v>
+        <v>0.09714514955170843</v>
       </c>
       <c r="C27">
-        <v>61.76659276723473</v>
+        <v>61.15245639177303</v>
       </c>
       <c r="D27">
-        <v>79.84159276723473</v>
+        <v>80.04645639177302</v>
       </c>
       <c r="E27">
-        <v>1.375</v>
+        <v>2.193999999999999</v>
       </c>
       <c r="F27">
-        <v>20.475</v>
+        <v>21.294</v>
       </c>
       <c r="G27">
         <v>2.4</v>
@@ -3742,28 +3742,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M27">
-        <v>1.1322675</v>
+        <v>1.1775582</v>
       </c>
       <c r="N27">
-        <v>4.530793724489796</v>
+        <v>4.485503024489796</v>
       </c>
       <c r="O27">
-        <v>0.9333435072448981</v>
+        <v>0.9240136230448981</v>
       </c>
       <c r="P27">
-        <v>3.597450217244898</v>
+        <v>3.561489401444899</v>
       </c>
       <c r="Q27">
-        <v>6.587450217244898</v>
+        <v>6.551489401444899</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1150664597830402</v>
+        <v>0.1158500237185249</v>
       </c>
       <c r="T27">
-        <v>1.59968729291086</v>
+        <v>1.617783457702654</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.001522365068144</v>
+        <v>4.809156120257832</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09714514955170843</v>
+        <v>0.09701340426613669</v>
       </c>
       <c r="C28">
-        <v>61.15245639177303</v>
+        <v>60.53937403008382</v>
       </c>
       <c r="D28">
-        <v>80.04645639177302</v>
+        <v>80.25237403008381</v>
       </c>
       <c r="E28">
-        <v>2.193999999999999</v>
+        <v>3.013000000000002</v>
       </c>
       <c r="F28">
-        <v>21.294</v>
+        <v>22.113</v>
       </c>
       <c r="G28">
         <v>2.4</v>
@@ -3824,28 +3824,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M28">
-        <v>1.1775582</v>
+        <v>1.2228489</v>
       </c>
       <c r="N28">
-        <v>4.485503024489796</v>
+        <v>4.440212324489796</v>
       </c>
       <c r="O28">
-        <v>0.9240136230448981</v>
+        <v>0.914683738844898</v>
       </c>
       <c r="P28">
-        <v>3.561489401444899</v>
+        <v>3.525528585644898</v>
       </c>
       <c r="Q28">
-        <v>6.551489401444899</v>
+        <v>6.515528585644898</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1158500237185249</v>
+        <v>0.1166550551590914</v>
       </c>
       <c r="T28">
-        <v>1.617783457702654</v>
+        <v>1.636375407831209</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.809156120257832</v>
+        <v>4.631039226914949</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3870,22 +3870,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09701340426613669</v>
+        <v>0.09743745898056494</v>
       </c>
       <c r="C29">
-        <v>60.53937403008382</v>
+        <v>59.06132925477208</v>
       </c>
       <c r="D29">
-        <v>80.25237403008381</v>
+        <v>79.59332925477207</v>
       </c>
       <c r="E29">
-        <v>3.013000000000002</v>
+        <v>3.832000000000001</v>
       </c>
       <c r="F29">
-        <v>22.113</v>
+        <v>22.932</v>
       </c>
       <c r="G29">
         <v>2.4</v>
@@ -3906,45 +3906,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M29">
-        <v>1.2228489</v>
+        <v>1.3254696</v>
       </c>
       <c r="N29">
-        <v>4.440212324489796</v>
+        <v>4.337591624489797</v>
       </c>
       <c r="O29">
-        <v>0.914683738844898</v>
+        <v>0.8935438746448982</v>
       </c>
       <c r="P29">
-        <v>3.525528585644898</v>
+        <v>3.444047749844898</v>
       </c>
       <c r="Q29">
-        <v>6.515528585644898</v>
+        <v>6.434047749844899</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1166550551590914</v>
+        <v>0.117482448584118</v>
       </c>
       <c r="T29">
-        <v>1.636375407831209</v>
+        <v>1.655483801018891</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.631039226914949</v>
+        <v>4.272494234865738</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3952,22 +3952,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09743745898056494</v>
+        <v>0.09732556369499321</v>
       </c>
       <c r="C30">
-        <v>59.06132925477208</v>
+        <v>58.41517779184558</v>
       </c>
       <c r="D30">
-        <v>79.59332925477207</v>
+        <v>79.76617779184558</v>
       </c>
       <c r="E30">
-        <v>3.832000000000001</v>
+        <v>4.651000000000003</v>
       </c>
       <c r="F30">
-        <v>22.932</v>
+        <v>23.751</v>
       </c>
       <c r="G30">
         <v>2.4</v>
@@ -3988,28 +3988,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M30">
-        <v>1.3254696</v>
+        <v>1.3728078</v>
       </c>
       <c r="N30">
-        <v>4.337591624489797</v>
+        <v>4.290253424489796</v>
       </c>
       <c r="O30">
-        <v>0.8935438746448982</v>
+        <v>0.8837922054448981</v>
       </c>
       <c r="P30">
-        <v>3.444047749844898</v>
+        <v>3.406461219044898</v>
       </c>
       <c r="Q30">
-        <v>6.434047749844899</v>
+        <v>6.396461219044898</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.117482448584118</v>
+        <v>0.1183331488661876</v>
       </c>
       <c r="T30">
-        <v>1.655483801018891</v>
+        <v>1.675130458803409</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.272494234865738</v>
+        <v>4.125166847456574</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09732556369499321</v>
+        <v>0.09804736840942146</v>
       </c>
       <c r="C31">
-        <v>58.41517779184558</v>
+        <v>56.49419687041617</v>
       </c>
       <c r="D31">
-        <v>79.76617779184558</v>
+        <v>78.66419687041616</v>
       </c>
       <c r="E31">
-        <v>4.651</v>
+        <v>5.469999999999999</v>
       </c>
       <c r="F31">
-        <v>23.751</v>
+        <v>24.57</v>
       </c>
       <c r="G31">
         <v>2.4</v>
@@ -4070,45 +4070,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M31">
-        <v>1.3728078</v>
+        <v>1.506141</v>
       </c>
       <c r="N31">
-        <v>4.290253424489796</v>
+        <v>4.156920224489797</v>
       </c>
       <c r="O31">
-        <v>0.8837922054448981</v>
+        <v>0.8563255662448982</v>
       </c>
       <c r="P31">
-        <v>3.406461219044898</v>
+        <v>3.300594658244899</v>
       </c>
       <c r="Q31">
-        <v>6.396461219044898</v>
+        <v>6.290594658244899</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1183331488661876</v>
+        <v>0.1192081548706021</v>
       </c>
       <c r="T31">
-        <v>1.675130458803409</v>
+        <v>1.695338449667485</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.125166847456574</v>
+        <v>3.759980788312513</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09804736840942146</v>
+        <v>0.09796326312384972</v>
       </c>
       <c r="C32">
-        <v>56.49419687041617</v>
+        <v>55.80203085943158</v>
       </c>
       <c r="D32">
-        <v>78.66419687041616</v>
+        <v>78.79103085943157</v>
       </c>
       <c r="E32">
-        <v>5.469999999999999</v>
+        <v>6.289000000000001</v>
       </c>
       <c r="F32">
-        <v>24.57</v>
+        <v>25.389</v>
       </c>
       <c r="G32">
         <v>2.4</v>
@@ -4152,28 +4152,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M32">
-        <v>1.506141</v>
+        <v>1.5563457</v>
       </c>
       <c r="N32">
-        <v>4.156920224489797</v>
+        <v>4.106715524489796</v>
       </c>
       <c r="O32">
-        <v>0.8563255662448982</v>
+        <v>0.8459833980448981</v>
       </c>
       <c r="P32">
-        <v>3.300594658244899</v>
+        <v>3.260732126444898</v>
       </c>
       <c r="Q32">
-        <v>6.290594658244899</v>
+        <v>6.250732126444898</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1192081548706021</v>
+        <v>0.1201085233678982</v>
       </c>
       <c r="T32">
-        <v>1.695338449667485</v>
+        <v>1.716132179397186</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.759980788312513</v>
+        <v>3.638691085463722</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4198,22 +4198,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09796326312384972</v>
+        <v>0.09787915783827797</v>
       </c>
       <c r="C33">
-        <v>55.80203085943158</v>
+        <v>55.11027450978982</v>
       </c>
       <c r="D33">
-        <v>78.79103085943157</v>
+        <v>78.91827450978981</v>
       </c>
       <c r="E33">
-        <v>6.289000000000001</v>
+        <v>7.108000000000001</v>
       </c>
       <c r="F33">
-        <v>25.389</v>
+        <v>26.208</v>
       </c>
       <c r="G33">
         <v>2.4</v>
@@ -4234,28 +4234,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M33">
-        <v>1.5563457</v>
+        <v>1.6065504</v>
       </c>
       <c r="N33">
-        <v>4.106715524489796</v>
+        <v>4.056510824489797</v>
       </c>
       <c r="O33">
-        <v>0.8459833980448981</v>
+        <v>0.8356412298448982</v>
       </c>
       <c r="P33">
-        <v>3.260732126444898</v>
+        <v>3.220869594644899</v>
       </c>
       <c r="Q33">
-        <v>6.250732126444898</v>
+        <v>6.210869594644899</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1201085233678982</v>
+        <v>0.1210353732915853</v>
       </c>
       <c r="T33">
-        <v>1.716132179397186</v>
+        <v>1.737537489413055</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.638691085463722</v>
+        <v>3.524981989042981</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09787915783827797</v>
+        <v>0.09852870855270622</v>
       </c>
       <c r="C34">
-        <v>55.11027450978982</v>
+        <v>53.31910160822824</v>
       </c>
       <c r="D34">
-        <v>78.91827450978981</v>
+        <v>77.94610160822823</v>
       </c>
       <c r="E34">
-        <v>7.108000000000001</v>
+        <v>7.927000000000003</v>
       </c>
       <c r="F34">
-        <v>26.208</v>
+        <v>27.027</v>
       </c>
       <c r="G34">
         <v>2.4</v>
@@ -4316,45 +4316,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M34">
-        <v>1.6065504</v>
+        <v>1.7324307</v>
       </c>
       <c r="N34">
-        <v>4.056510824489797</v>
+        <v>3.930630524489796</v>
       </c>
       <c r="O34">
-        <v>0.8356412298448982</v>
+        <v>0.8097098880448981</v>
       </c>
       <c r="P34">
-        <v>3.220869594644899</v>
+        <v>3.120920636444898</v>
       </c>
       <c r="Q34">
-        <v>6.210869594644899</v>
+        <v>6.110920636444899</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1210353732915853</v>
+        <v>0.1219898903771735</v>
       </c>
       <c r="T34">
-        <v>1.737537489413055</v>
+        <v>1.759581763907009</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.524981989042981</v>
+        <v>3.268852961616182</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4362,22 +4362,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09852870855270622</v>
+        <v>0.0984668352671345</v>
       </c>
       <c r="C35">
-        <v>53.31910160822824</v>
+        <v>52.59167311389298</v>
       </c>
       <c r="D35">
-        <v>77.94610160822823</v>
+        <v>78.03767311389298</v>
       </c>
       <c r="E35">
-        <v>7.927000000000003</v>
+        <v>8.746000000000002</v>
       </c>
       <c r="F35">
-        <v>27.027</v>
+        <v>27.846</v>
       </c>
       <c r="G35">
         <v>2.4</v>
@@ -4398,28 +4398,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M35">
-        <v>1.7324307</v>
+        <v>1.7849286</v>
       </c>
       <c r="N35">
-        <v>3.930630524489796</v>
+        <v>3.878132624489796</v>
       </c>
       <c r="O35">
-        <v>0.8097098880448981</v>
+        <v>0.798895320644898</v>
       </c>
       <c r="P35">
-        <v>3.120920636444898</v>
+        <v>3.079237303844898</v>
       </c>
       <c r="Q35">
-        <v>6.110920636444899</v>
+        <v>6.069237303844898</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1219898903771735</v>
+        <v>0.1229733322229311</v>
       </c>
       <c r="T35">
-        <v>1.759581763907009</v>
+        <v>1.782294046718962</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.268852961616182</v>
+        <v>3.172710227451</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0984668352671345</v>
+        <v>0.09840496198156276</v>
       </c>
       <c r="C36">
-        <v>52.59167311389298</v>
+        <v>51.8644600300326</v>
       </c>
       <c r="D36">
-        <v>78.03767311389298</v>
+        <v>78.1294600300326</v>
       </c>
       <c r="E36">
-        <v>8.746000000000002</v>
+        <v>9.565000000000005</v>
       </c>
       <c r="F36">
-        <v>27.846</v>
+        <v>28.66500000000001</v>
       </c>
       <c r="G36">
         <v>2.4</v>
@@ -4480,28 +4480,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M36">
-        <v>1.7849286</v>
+        <v>1.837426500000001</v>
       </c>
       <c r="N36">
-        <v>3.878132624489796</v>
+        <v>3.825634724489796</v>
       </c>
       <c r="O36">
-        <v>0.798895320644898</v>
+        <v>0.788080753244898</v>
       </c>
       <c r="P36">
-        <v>3.079237303844898</v>
+        <v>3.037553971244898</v>
       </c>
       <c r="Q36">
-        <v>6.069237303844898</v>
+        <v>6.027553971244899</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1229733322229311</v>
+        <v>0.1239870338177889</v>
       </c>
       <c r="T36">
-        <v>1.782294046718962</v>
+        <v>1.805705169002052</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.172710227451</v>
+        <v>3.082061363809543</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09840496198156276</v>
+        <v>0.100572640695991</v>
       </c>
       <c r="C37">
-        <v>51.8644600300326</v>
+        <v>47.95341324673281</v>
       </c>
       <c r="D37">
-        <v>78.1294600300326</v>
+        <v>75.03741324673281</v>
       </c>
       <c r="E37">
-        <v>9.565000000000005</v>
+        <v>10.384</v>
       </c>
       <c r="F37">
-        <v>28.66500000000001</v>
+        <v>29.48400000000001</v>
       </c>
       <c r="G37">
         <v>2.4</v>
@@ -4562,45 +4562,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M37">
-        <v>1.837426500000001</v>
+        <v>2.119899600000001</v>
       </c>
       <c r="N37">
-        <v>3.825634724489796</v>
+        <v>3.543161624489796</v>
       </c>
       <c r="O37">
-        <v>0.788080753244898</v>
+        <v>0.729891294644898</v>
       </c>
       <c r="P37">
-        <v>3.037553971244898</v>
+        <v>2.813270329844898</v>
       </c>
       <c r="Q37">
-        <v>6.027553971244899</v>
+        <v>5.803270329844898</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1239870338177889</v>
+        <v>0.125032413587486</v>
       </c>
       <c r="T37">
-        <v>1.805705169002052</v>
+        <v>1.829847888856489</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.082061363809543</v>
+        <v>2.671381807180771</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.100572640695991</v>
+        <v>0.1005726994104193</v>
       </c>
       <c r="C38">
-        <v>47.9534132467328</v>
+        <v>47.13433280923631</v>
       </c>
       <c r="D38">
-        <v>75.0374132467328</v>
+        <v>75.0373328092363</v>
       </c>
       <c r="E38">
-        <v>10.384</v>
+        <v>11.203</v>
       </c>
       <c r="F38">
-        <v>29.484</v>
+        <v>30.303</v>
       </c>
       <c r="G38">
         <v>2.4</v>
@@ -4644,28 +4644,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M38">
-        <v>2.1198996</v>
+        <v>2.1787857</v>
       </c>
       <c r="N38">
-        <v>3.543161624489796</v>
+        <v>3.484275524489796</v>
       </c>
       <c r="O38">
-        <v>0.7298912946448981</v>
+        <v>0.7177607580448981</v>
       </c>
       <c r="P38">
-        <v>2.813270329844898</v>
+        <v>2.766514766444898</v>
       </c>
       <c r="Q38">
-        <v>5.803270329844898</v>
+        <v>5.756514766444898</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.125032413587486</v>
+        <v>0.1261109800165385</v>
       </c>
       <c r="T38">
-        <v>1.829847888856489</v>
+        <v>1.854757044261859</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.671381807180772</v>
+        <v>2.599182298878589</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4690,22 +4690,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1005726994104193</v>
+        <v>0.1005727581248475</v>
       </c>
       <c r="C39">
-        <v>47.13433280923631</v>
+        <v>46.31525237191228</v>
       </c>
       <c r="D39">
-        <v>75.0373328092363</v>
+        <v>75.03725237191227</v>
       </c>
       <c r="E39">
-        <v>11.203</v>
+        <v>12.022</v>
       </c>
       <c r="F39">
-        <v>30.303</v>
+        <v>31.122</v>
       </c>
       <c r="G39">
         <v>2.4</v>
@@ -4726,28 +4726,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M39">
-        <v>2.1787857</v>
+        <v>2.2376718</v>
       </c>
       <c r="N39">
-        <v>3.484275524489796</v>
+        <v>3.425389424489796</v>
       </c>
       <c r="O39">
-        <v>0.7177607580448981</v>
+        <v>0.7056302214448981</v>
       </c>
       <c r="P39">
-        <v>2.766514766444898</v>
+        <v>2.719759203044898</v>
       </c>
       <c r="Q39">
-        <v>5.756514766444898</v>
+        <v>5.709759203044898</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1261109800165385</v>
+        <v>0.1272243389110444</v>
       </c>
       <c r="T39">
-        <v>1.854757044261859</v>
+        <v>1.880469720809339</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.599182298878589</v>
+        <v>2.530782764697574</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4772,22 +4772,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1005727581248475</v>
+        <v>0.1017804908392758</v>
       </c>
       <c r="C40">
-        <v>46.31525237191228</v>
+        <v>43.8773858144439</v>
       </c>
       <c r="D40">
-        <v>75.03725237191227</v>
+        <v>73.41838581444389</v>
       </c>
       <c r="E40">
-        <v>12.022</v>
+        <v>12.841</v>
       </c>
       <c r="F40">
-        <v>31.122</v>
+        <v>31.941</v>
       </c>
       <c r="G40">
         <v>2.4</v>
@@ -4808,45 +4808,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M40">
-        <v>2.2376718</v>
+        <v>2.4211278</v>
       </c>
       <c r="N40">
-        <v>3.425389424489796</v>
+        <v>3.241933424489796</v>
       </c>
       <c r="O40">
-        <v>0.7056302214448981</v>
+        <v>0.6678382854448981</v>
       </c>
       <c r="P40">
-        <v>2.719759203044898</v>
+        <v>2.574095139044898</v>
       </c>
       <c r="Q40">
-        <v>5.709759203044898</v>
+        <v>5.564095139044898</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1272243389110444</v>
+        <v>0.1283742013758619</v>
       </c>
       <c r="T40">
-        <v>1.880469720809339</v>
+        <v>1.907025435932147</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.530782764697574</v>
+        <v>2.339017884347037</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4854,22 +4854,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1017804908392758</v>
+        <v>0.101811515553704</v>
       </c>
       <c r="C41">
-        <v>43.8773858144439</v>
+        <v>43.01771945447918</v>
       </c>
       <c r="D41">
-        <v>73.41838581444389</v>
+        <v>73.37771945447918</v>
       </c>
       <c r="E41">
-        <v>12.841</v>
+        <v>13.66</v>
       </c>
       <c r="F41">
-        <v>31.941</v>
+        <v>32.76000000000001</v>
       </c>
       <c r="G41">
         <v>2.4</v>
@@ -4890,28 +4890,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M41">
-        <v>2.4211278</v>
+        <v>2.483208000000001</v>
       </c>
       <c r="N41">
-        <v>3.241933424489796</v>
+        <v>3.179853224489796</v>
       </c>
       <c r="O41">
-        <v>0.6678382854448981</v>
+        <v>0.6550497642448979</v>
       </c>
       <c r="P41">
-        <v>2.574095139044898</v>
+        <v>2.524803460244898</v>
       </c>
       <c r="Q41">
-        <v>5.564095139044898</v>
+        <v>5.514803460244898</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1283742013758619</v>
+        <v>0.1295623925895067</v>
       </c>
       <c r="T41">
-        <v>1.907025435932147</v>
+        <v>1.934466341559047</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.339017884347037</v>
+        <v>2.280542437238361</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4936,22 +4936,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.101811515553704</v>
+        <v>0.1018425402681323</v>
       </c>
       <c r="C42">
-        <v>43.01771945447918</v>
+        <v>42.15809811967564</v>
       </c>
       <c r="D42">
-        <v>73.37771945447918</v>
+        <v>73.33709811967564</v>
       </c>
       <c r="E42">
-        <v>13.66</v>
+        <v>14.47900000000001</v>
       </c>
       <c r="F42">
-        <v>32.76000000000001</v>
+        <v>33.57900000000001</v>
       </c>
       <c r="G42">
         <v>2.4</v>
@@ -4972,28 +4972,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M42">
-        <v>2.483208000000001</v>
+        <v>2.545288200000001</v>
       </c>
       <c r="N42">
-        <v>3.179853224489796</v>
+        <v>3.117773024489796</v>
       </c>
       <c r="O42">
-        <v>0.6550497642448979</v>
+        <v>0.642261243044898</v>
       </c>
       <c r="P42">
-        <v>2.524803460244898</v>
+        <v>2.475511781444898</v>
       </c>
       <c r="Q42">
-        <v>5.514803460244898</v>
+        <v>5.465511781444897</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1295623925895067</v>
+        <v>0.1307908614714107</v>
       </c>
       <c r="T42">
-        <v>1.934466341559047</v>
+        <v>1.96283744737669</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.280542437238361</v>
+        <v>2.224919450964254</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5018,22 +5018,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1018425402681323</v>
+        <v>0.1018735649825606</v>
       </c>
       <c r="C43">
-        <v>42.15809811967564</v>
+        <v>41.29852173529796</v>
       </c>
       <c r="D43">
-        <v>73.33709811967564</v>
+        <v>73.29652173529796</v>
       </c>
       <c r="E43">
-        <v>14.47900000000001</v>
+        <v>15.298</v>
       </c>
       <c r="F43">
-        <v>33.57900000000001</v>
+        <v>34.398</v>
       </c>
       <c r="G43">
         <v>2.4</v>
@@ -5054,28 +5054,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M43">
-        <v>2.545288200000001</v>
+        <v>2.6073684</v>
       </c>
       <c r="N43">
-        <v>3.117773024489796</v>
+        <v>3.055692824489796</v>
       </c>
       <c r="O43">
-        <v>0.642261243044898</v>
+        <v>0.629472721844898</v>
       </c>
       <c r="P43">
-        <v>2.475511781444898</v>
+        <v>2.426220102644898</v>
       </c>
       <c r="Q43">
-        <v>5.465511781444897</v>
+        <v>5.416220102644898</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1307908614714107</v>
+        <v>0.1320616913492424</v>
       </c>
       <c r="T43">
-        <v>1.96283744737669</v>
+        <v>1.992186867188045</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.224919450964254</v>
+        <v>2.171945178322249</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5100,22 +5100,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1018735649825606</v>
+        <v>0.1019045896969888</v>
       </c>
       <c r="C44">
-        <v>41.29852173529796</v>
+        <v>40.43899022677604</v>
       </c>
       <c r="D44">
-        <v>73.29652173529796</v>
+        <v>73.25599022677604</v>
       </c>
       <c r="E44">
-        <v>15.298</v>
+        <v>16.117</v>
       </c>
       <c r="F44">
-        <v>34.398</v>
+        <v>35.217</v>
       </c>
       <c r="G44">
         <v>2.4</v>
@@ -5136,28 +5136,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M44">
-        <v>2.6073684</v>
+        <v>2.6694486</v>
       </c>
       <c r="N44">
-        <v>3.055692824489796</v>
+        <v>2.993612624489796</v>
       </c>
       <c r="O44">
-        <v>0.629472721844898</v>
+        <v>0.6166842006448982</v>
       </c>
       <c r="P44">
-        <v>2.426220102644898</v>
+        <v>2.376928423844898</v>
       </c>
       <c r="Q44">
-        <v>5.416220102644898</v>
+        <v>5.366928423844898</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1320616913492423</v>
+        <v>0.1333771117491032</v>
       </c>
       <c r="T44">
-        <v>1.992186867188045</v>
+        <v>2.022566091203307</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.171945178322249</v>
+        <v>2.12143482533801</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5182,22 +5182,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1019045896969888</v>
+        <v>0.1019356144114171</v>
       </c>
       <c r="C45">
-        <v>40.43899022677604</v>
+        <v>39.57950351970466</v>
       </c>
       <c r="D45">
-        <v>73.25599022677604</v>
+        <v>73.21550351970465</v>
       </c>
       <c r="E45">
-        <v>16.117</v>
+        <v>16.936</v>
       </c>
       <c r="F45">
-        <v>35.217</v>
+        <v>36.036</v>
       </c>
       <c r="G45">
         <v>2.4</v>
@@ -5218,28 +5218,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M45">
-        <v>2.6694486</v>
+        <v>2.7315288</v>
       </c>
       <c r="N45">
-        <v>2.993612624489796</v>
+        <v>2.931532424489796</v>
       </c>
       <c r="O45">
-        <v>0.6166842006448982</v>
+        <v>0.603895679444898</v>
       </c>
       <c r="P45">
-        <v>2.376928423844898</v>
+        <v>2.327636745044898</v>
       </c>
       <c r="Q45">
-        <v>5.366928423844898</v>
+        <v>5.317636745044898</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1333771117491032</v>
+        <v>0.1347395114489591</v>
       </c>
       <c r="T45">
-        <v>2.022566091203307</v>
+        <v>2.054030287504828</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.12143482533801</v>
+        <v>2.073220397489419</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1019356144114171</v>
+        <v>0.1019666391258453</v>
       </c>
       <c r="C46">
-        <v>39.57950351970466</v>
+        <v>38.72006153984312</v>
       </c>
       <c r="D46">
-        <v>73.21550351970465</v>
+        <v>73.17506153984311</v>
       </c>
       <c r="E46">
-        <v>16.936</v>
+        <v>17.755</v>
       </c>
       <c r="F46">
-        <v>36.036</v>
+        <v>36.855</v>
       </c>
       <c r="G46">
         <v>2.4</v>
@@ -5300,28 +5300,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M46">
-        <v>2.7315288</v>
+        <v>2.793609</v>
       </c>
       <c r="N46">
-        <v>2.931532424489796</v>
+        <v>2.869452224489796</v>
       </c>
       <c r="O46">
-        <v>0.603895679444898</v>
+        <v>0.591107158244898</v>
       </c>
       <c r="P46">
-        <v>2.327636745044898</v>
+        <v>2.278345066244898</v>
       </c>
       <c r="Q46">
-        <v>5.317636745044898</v>
+        <v>5.268345066244898</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1347395114489591</v>
+        <v>0.1361514529560824</v>
       </c>
       <c r="T46">
-        <v>2.054030287504828</v>
+        <v>2.086638636399132</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.073220397489419</v>
+        <v>2.027148833100765</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5346,22 +5346,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1019666391258453</v>
+        <v>0.1071840718402736</v>
       </c>
       <c r="C47">
-        <v>38.72006153984312</v>
+        <v>31.681435690458</v>
       </c>
       <c r="D47">
-        <v>73.17506153984311</v>
+        <v>66.955435690458</v>
       </c>
       <c r="E47">
-        <v>17.755</v>
+        <v>18.57400000000001</v>
       </c>
       <c r="F47">
-        <v>36.855</v>
+        <v>37.67400000000001</v>
       </c>
       <c r="G47">
         <v>2.4</v>
@@ -5382,45 +5382,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M47">
-        <v>2.793609</v>
+        <v>3.39066</v>
       </c>
       <c r="N47">
-        <v>2.869452224489796</v>
+        <v>2.272401224489796</v>
       </c>
       <c r="O47">
-        <v>0.591107158244898</v>
+        <v>0.468114652244898</v>
       </c>
       <c r="P47">
-        <v>2.278345066244898</v>
+        <v>1.804286572244898</v>
       </c>
       <c r="Q47">
-        <v>5.268345066244898</v>
+        <v>4.794286572244898</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1361514529560824</v>
+        <v>0.1376156885930992</v>
       </c>
       <c r="T47">
-        <v>2.086638636399132</v>
+        <v>2.120454701919151</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.206</v>
       </c>
       <c r="W47">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.027148833100765</v>
+        <v>1.670194364663457</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5428,22 +5428,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1071840718402736</v>
+        <v>0.1073278445547018</v>
       </c>
       <c r="C48">
-        <v>31.681435690458</v>
+        <v>30.70598027088963</v>
       </c>
       <c r="D48">
-        <v>66.955435690458</v>
+        <v>66.79898027088963</v>
       </c>
       <c r="E48">
-        <v>18.57400000000001</v>
+        <v>19.393</v>
       </c>
       <c r="F48">
-        <v>37.67400000000001</v>
+        <v>38.493</v>
       </c>
       <c r="G48">
         <v>2.4</v>
@@ -5464,28 +5464,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M48">
-        <v>3.39066</v>
+        <v>3.46437</v>
       </c>
       <c r="N48">
-        <v>2.272401224489796</v>
+        <v>2.198691224489796</v>
       </c>
       <c r="O48">
-        <v>0.468114652244898</v>
+        <v>0.4529303922448981</v>
       </c>
       <c r="P48">
-        <v>1.804286572244898</v>
+        <v>1.745760832244898</v>
       </c>
       <c r="Q48">
-        <v>4.794286572244898</v>
+        <v>4.735760832244898</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1376156885930992</v>
+        <v>0.1391351784050978</v>
       </c>
       <c r="T48">
-        <v>2.120454701919151</v>
+        <v>2.155546845383322</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.670194364663457</v>
+        <v>1.634658314351468</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1073278445547018</v>
+        <v>0.1074716172691301</v>
       </c>
       <c r="C49">
-        <v>30.70598027088963</v>
+        <v>29.73125432855417</v>
       </c>
       <c r="D49">
-        <v>66.79898027088963</v>
+        <v>66.64325432855416</v>
       </c>
       <c r="E49">
-        <v>19.393</v>
+        <v>20.212</v>
       </c>
       <c r="F49">
-        <v>38.493</v>
+        <v>39.312</v>
       </c>
       <c r="G49">
         <v>2.4</v>
@@ -5546,28 +5546,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M49">
-        <v>3.46437</v>
+        <v>3.53808</v>
       </c>
       <c r="N49">
-        <v>2.198691224489796</v>
+        <v>2.124981224489796</v>
       </c>
       <c r="O49">
-        <v>0.4529303922448981</v>
+        <v>0.4377461322448981</v>
       </c>
       <c r="P49">
-        <v>1.745760832244898</v>
+        <v>1.687235092244898</v>
       </c>
       <c r="Q49">
-        <v>4.735760832244898</v>
+        <v>4.677235092244898</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1391351784050978</v>
+        <v>0.1407131101329425</v>
       </c>
       <c r="T49">
-        <v>2.155546845383322</v>
+        <v>2.191988686673037</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.634658314351468</v>
+        <v>1.600602932802479</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5592,22 +5592,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1074716172691301</v>
+        <v>0.1076153899835584</v>
       </c>
       <c r="C50">
-        <v>29.73125432855421</v>
+        <v>28.75725277350946</v>
       </c>
       <c r="D50">
-        <v>66.64325432855421</v>
+        <v>66.48825277350946</v>
       </c>
       <c r="E50">
-        <v>20.212</v>
+        <v>21.031</v>
       </c>
       <c r="F50">
-        <v>39.312</v>
+        <v>40.131</v>
       </c>
       <c r="G50">
         <v>2.4</v>
@@ -5628,28 +5628,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M50">
-        <v>3.53808</v>
+        <v>3.61179</v>
       </c>
       <c r="N50">
-        <v>2.124981224489796</v>
+        <v>2.051271224489796</v>
       </c>
       <c r="O50">
-        <v>0.4377461322448981</v>
+        <v>0.4225618722448981</v>
       </c>
       <c r="P50">
-        <v>1.687235092244898</v>
+        <v>1.628709352244898</v>
       </c>
       <c r="Q50">
-        <v>4.677235092244898</v>
+        <v>4.618709352244899</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1407131101329425</v>
+        <v>0.142352921536389</v>
       </c>
       <c r="T50">
-        <v>2.191988686673037</v>
+        <v>2.229859619778036</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.600602932802479</v>
+        <v>1.567937566826919</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5674,22 +5674,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1076153899835584</v>
+        <v>0.1077591626979866</v>
       </c>
       <c r="C51">
-        <v>28.75725277350946</v>
+        <v>27.78397056305683</v>
       </c>
       <c r="D51">
-        <v>66.48825277350946</v>
+        <v>66.33397056305682</v>
       </c>
       <c r="E51">
-        <v>21.031</v>
+        <v>21.85</v>
       </c>
       <c r="F51">
-        <v>40.131</v>
+        <v>40.95</v>
       </c>
       <c r="G51">
         <v>2.4</v>
@@ -5710,28 +5710,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M51">
-        <v>3.61179</v>
+        <v>3.6855</v>
       </c>
       <c r="N51">
-        <v>2.051271224489796</v>
+        <v>1.977561224489796</v>
       </c>
       <c r="O51">
-        <v>0.4225618722448981</v>
+        <v>0.407377612244898</v>
       </c>
       <c r="P51">
-        <v>1.628709352244898</v>
+        <v>1.570183612244898</v>
       </c>
       <c r="Q51">
-        <v>4.618709352244899</v>
+        <v>4.560183612244899</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.142352921536389</v>
+        <v>0.1440583253959732</v>
       </c>
       <c r="T51">
-        <v>2.229859619778036</v>
+        <v>2.269245390207234</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.567937566826919</v>
+        <v>1.53657881549038</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5756,22 +5756,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1077591626979866</v>
+        <v>0.1079029354124149</v>
       </c>
       <c r="C52">
-        <v>27.78397056305683</v>
+        <v>26.81140270119454</v>
       </c>
       <c r="D52">
-        <v>66.33397056305682</v>
+        <v>66.18040270119454</v>
       </c>
       <c r="E52">
-        <v>21.85</v>
+        <v>22.669</v>
       </c>
       <c r="F52">
-        <v>40.95</v>
+        <v>41.76900000000001</v>
       </c>
       <c r="G52">
         <v>2.4</v>
@@ -5792,28 +5792,28 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M52">
-        <v>3.6855</v>
+        <v>3.75921</v>
       </c>
       <c r="N52">
-        <v>1.977561224489796</v>
+        <v>1.903851224489796</v>
       </c>
       <c r="O52">
-        <v>0.407377612244898</v>
+        <v>0.392193352244898</v>
       </c>
       <c r="P52">
-        <v>1.570183612244898</v>
+        <v>1.511657872244898</v>
       </c>
       <c r="Q52">
-        <v>4.560183612244899</v>
+        <v>4.501657872244898</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1440583253959732</v>
+        <v>0.1458333375763569</v>
       </c>
       <c r="T52">
-        <v>2.269245390207234</v>
+        <v>2.310238743102931</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.53657881549038</v>
+        <v>1.506449819108216</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5838,22 +5838,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1079029354124149</v>
+        <v>0.1335320266724772</v>
       </c>
       <c r="C53">
-        <v>26.81140270119454</v>
+        <v>6.659171214491671</v>
       </c>
       <c r="D53">
-        <v>66.18040270119454</v>
+        <v>46.84717121449167</v>
       </c>
       <c r="E53">
-        <v>22.669</v>
+        <v>23.488</v>
       </c>
       <c r="F53">
-        <v>41.76900000000001</v>
+        <v>42.588</v>
       </c>
       <c r="G53">
         <v>2.4</v>
@@ -5874,45 +5874,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M53">
-        <v>3.75921</v>
+        <v>6.251918400000001</v>
       </c>
       <c r="N53">
-        <v>1.903851224489796</v>
+        <v>-0.5888571755102046</v>
       </c>
       <c r="O53">
-        <v>0.392193352244898</v>
+        <v>-0.1213045781551021</v>
       </c>
       <c r="P53">
-        <v>1.511657872244898</v>
+        <v>-0.4675525973551024</v>
       </c>
       <c r="Q53">
-        <v>4.501657872244898</v>
+        <v>2.522447402644898</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1458333375763569</v>
+        <v>0.1488335672751522</v>
       </c>
       <c r="T53">
-        <v>2.310238743102931</v>
+        <v>2.37952811259012</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.206</v>
+        <v>0.1865972230611484</v>
       </c>
       <c r="W53">
-        <v>0.07146</v>
+        <v>0.1194075276546234</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.506449819108216</v>
+        <v>0.9058117624327591</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1335320266724772</v>
+        <v>0.1345420266724772</v>
       </c>
       <c r="C54">
-        <v>6.659171214491671</v>
+        <v>5.306989308456728</v>
       </c>
       <c r="D54">
-        <v>46.84717121449167</v>
+        <v>46.31398930845673</v>
       </c>
       <c r="E54">
-        <v>23.488</v>
+        <v>24.307</v>
       </c>
       <c r="F54">
-        <v>42.588</v>
+        <v>43.407</v>
       </c>
       <c r="G54">
         <v>2.4</v>
@@ -5956,37 +5956,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M54">
-        <v>6.251918400000001</v>
+        <v>6.372147600000001</v>
       </c>
       <c r="N54">
-        <v>-0.5888571755102046</v>
+        <v>-0.7090863755102044</v>
       </c>
       <c r="O54">
-        <v>-0.1213045781551021</v>
+        <v>-0.1460717933551021</v>
       </c>
       <c r="P54">
-        <v>-0.4675525973551024</v>
+        <v>-0.5630145821551023</v>
       </c>
       <c r="Q54">
-        <v>2.522447402644898</v>
+        <v>2.426985417844898</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1488335672751522</v>
+        <v>0.151025770834198</v>
       </c>
       <c r="T54">
-        <v>2.37952811259012</v>
+        <v>2.430156370304803</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1865972230611484</v>
+        <v>0.1830765207392399</v>
       </c>
       <c r="W54">
-        <v>0.1194075276546234</v>
+        <v>0.1199243667554796</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9058117624327591</v>
+        <v>0.8887209744623298</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6002,22 +6002,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1345420266724772</v>
+        <v>0.1355520266724772</v>
       </c>
       <c r="C55">
-        <v>5.306989308456728</v>
+        <v>3.966807437296971</v>
       </c>
       <c r="D55">
-        <v>46.31398930845673</v>
+        <v>45.79280743729698</v>
       </c>
       <c r="E55">
-        <v>24.307</v>
+        <v>25.126</v>
       </c>
       <c r="F55">
-        <v>43.407</v>
+        <v>44.22600000000001</v>
       </c>
       <c r="G55">
         <v>2.4</v>
@@ -6038,37 +6038,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M55">
-        <v>6.372147600000001</v>
+        <v>6.492376800000002</v>
       </c>
       <c r="N55">
-        <v>-0.7090863755102044</v>
+        <v>-0.8293155755102051</v>
       </c>
       <c r="O55">
-        <v>-0.1460717933551021</v>
+        <v>-0.1708390085551023</v>
       </c>
       <c r="P55">
-        <v>-0.5630145821551023</v>
+        <v>-0.6584765669551028</v>
       </c>
       <c r="Q55">
-        <v>2.426985417844898</v>
+        <v>2.331523433044898</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.151025770834198</v>
+        <v>0.1533132875914631</v>
       </c>
       <c r="T55">
-        <v>2.430156370304803</v>
+        <v>2.482985856615777</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1830765207392399</v>
+        <v>0.1796862147996244</v>
       </c>
       <c r="W55">
-        <v>0.1199243667554796</v>
+        <v>0.1204220636674152</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8887209744623298</v>
+        <v>0.8722631786389532</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6084,22 +6084,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1355520266724772</v>
+        <v>0.1365620266724772</v>
       </c>
       <c r="C56">
-        <v>3.966807437296971</v>
+        <v>2.63822499178184</v>
       </c>
       <c r="D56">
-        <v>45.79280743729698</v>
+        <v>45.28322499178185</v>
       </c>
       <c r="E56">
-        <v>25.126</v>
+        <v>25.94500000000001</v>
       </c>
       <c r="F56">
-        <v>44.22600000000001</v>
+        <v>45.04500000000001</v>
       </c>
       <c r="G56">
         <v>2.4</v>
@@ -6120,37 +6120,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M56">
-        <v>6.492376800000002</v>
+        <v>6.612606000000002</v>
       </c>
       <c r="N56">
-        <v>-0.8293155755102051</v>
+        <v>-0.9495447755102058</v>
       </c>
       <c r="O56">
-        <v>-0.1708390085551023</v>
+        <v>-0.1956062237551024</v>
       </c>
       <c r="P56">
-        <v>-0.6584765669551028</v>
+        <v>-0.7539385517551034</v>
       </c>
       <c r="Q56">
-        <v>2.331523433044898</v>
+        <v>2.236061448244897</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1533132875914631</v>
+        <v>0.1557024717601623</v>
       </c>
       <c r="T56">
-        <v>2.482985856615777</v>
+        <v>2.538163320096128</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1796862147996244</v>
+        <v>0.1764191927123585</v>
       </c>
       <c r="W56">
-        <v>0.1204220636674152</v>
+        <v>0.1209016625098258</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8722631786389532</v>
+        <v>0.8564038481182449</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6166,22 +6166,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1365620266724772</v>
+        <v>0.1375720266724772</v>
       </c>
       <c r="C57">
-        <v>2.63822499178184</v>
+        <v>1.320858998352023</v>
       </c>
       <c r="D57">
-        <v>45.28322499178185</v>
+        <v>44.78485899835203</v>
       </c>
       <c r="E57">
-        <v>25.94500000000001</v>
+        <v>26.764</v>
       </c>
       <c r="F57">
-        <v>45.04500000000001</v>
+        <v>45.864</v>
       </c>
       <c r="G57">
         <v>2.4</v>
@@ -6202,37 +6202,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M57">
-        <v>6.612606000000002</v>
+        <v>6.732835200000001</v>
       </c>
       <c r="N57">
-        <v>-0.9495447755102058</v>
+        <v>-1.069773975510205</v>
       </c>
       <c r="O57">
-        <v>-0.1956062237551024</v>
+        <v>-0.2203734389551022</v>
       </c>
       <c r="P57">
-        <v>-0.7539385517551034</v>
+        <v>-0.8494005365551025</v>
       </c>
       <c r="Q57">
-        <v>2.236061448244897</v>
+        <v>2.140599463444897</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1557024717601623</v>
+        <v>0.1582002552092569</v>
       </c>
       <c r="T57">
-        <v>2.538163320096128</v>
+        <v>2.595848850098312</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1764191927123585</v>
+        <v>0.1732688499853521</v>
       </c>
       <c r="W57">
-        <v>0.1209016625098258</v>
+        <v>0.1213641328221503</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8564038481182449</v>
+        <v>0.8411109222589906</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1375720266724772</v>
+        <v>0.1385820266724772</v>
       </c>
       <c r="C58">
-        <v>1.320858998352023</v>
+        <v>0.01434315923363272</v>
       </c>
       <c r="D58">
-        <v>44.78485899835203</v>
+        <v>44.29734315923364</v>
       </c>
       <c r="E58">
-        <v>26.764</v>
+        <v>27.58300000000001</v>
       </c>
       <c r="F58">
-        <v>45.864</v>
+        <v>46.68300000000001</v>
       </c>
       <c r="G58">
         <v>2.4</v>
@@ -6284,37 +6284,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M58">
-        <v>6.732835200000001</v>
+        <v>6.853064400000002</v>
       </c>
       <c r="N58">
-        <v>-1.069773975510205</v>
+        <v>-1.190003175510205</v>
       </c>
       <c r="O58">
-        <v>-0.2203734389551022</v>
+        <v>-0.2451406541551023</v>
       </c>
       <c r="P58">
-        <v>-0.8494005365551025</v>
+        <v>-0.9448625213551031</v>
       </c>
       <c r="Q58">
-        <v>2.140599463444897</v>
+        <v>2.045137478644897</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1582002552092569</v>
+        <v>0.160814214632728</v>
       </c>
       <c r="T58">
-        <v>2.595848850098312</v>
+        <v>2.656217428007575</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1732688499853521</v>
+        <v>0.1702290455996441</v>
       </c>
       <c r="W58">
-        <v>0.1213641328221503</v>
+        <v>0.1218103761059723</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8411109222589906</v>
+        <v>0.8263545902895346</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6330,22 +6330,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1385820266724772</v>
+        <v>0.1395920266724772</v>
       </c>
       <c r="C59">
-        <v>0.01434315923363272</v>
+        <v>-1.281673045427979</v>
       </c>
       <c r="D59">
-        <v>44.29734315923364</v>
+        <v>43.82032695457203</v>
       </c>
       <c r="E59">
-        <v>27.58300000000001</v>
+        <v>28.40200000000001</v>
       </c>
       <c r="F59">
-        <v>46.68300000000001</v>
+        <v>47.50200000000001</v>
       </c>
       <c r="G59">
         <v>2.4</v>
@@ -6366,37 +6366,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M59">
-        <v>6.853064400000002</v>
+        <v>6.973293600000002</v>
       </c>
       <c r="N59">
-        <v>-1.190003175510205</v>
+        <v>-1.310232375510205</v>
       </c>
       <c r="O59">
-        <v>-0.2451406541551023</v>
+        <v>-0.2699078693551023</v>
       </c>
       <c r="P59">
-        <v>-0.9448625213551031</v>
+        <v>-1.040324506155103</v>
       </c>
       <c r="Q59">
-        <v>2.045137478644897</v>
+        <v>1.949675493844897</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.160814214632728</v>
+        <v>0.1635526483144596</v>
       </c>
       <c r="T59">
-        <v>2.656217428007575</v>
+        <v>2.719460700102994</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1702290455996441</v>
+        <v>0.1672940620548227</v>
       </c>
       <c r="W59">
-        <v>0.1218103761059723</v>
+        <v>0.122241231690352</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8263545902895346</v>
+        <v>0.8121070973535081</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6412,22 +6412,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1395920266724772</v>
+        <v>0.1738912019362374</v>
       </c>
       <c r="C60">
-        <v>-1.281673045427972</v>
+        <v>-13.83450840344358</v>
       </c>
       <c r="D60">
-        <v>43.82032695457203</v>
+        <v>32.08649159655642</v>
       </c>
       <c r="E60">
-        <v>28.402</v>
+        <v>29.221</v>
       </c>
       <c r="F60">
-        <v>47.502</v>
+        <v>48.321</v>
       </c>
       <c r="G60">
         <v>2.4</v>
@@ -6448,45 +6448,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M60">
-        <v>6.973293600000001</v>
+        <v>9.702856799999999</v>
       </c>
       <c r="N60">
-        <v>-1.310232375510204</v>
+        <v>-4.039795575510203</v>
       </c>
       <c r="O60">
-        <v>-0.2699078693551021</v>
+        <v>-0.8321978885551019</v>
       </c>
       <c r="P60">
-        <v>-1.040324506155102</v>
+        <v>-3.207597686955101</v>
       </c>
       <c r="Q60">
-        <v>1.949675493844898</v>
+        <v>-0.2175976869551008</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1635526483144596</v>
+        <v>0.1699104574532516</v>
       </c>
       <c r="T60">
-        <v>2.719460700102994</v>
+        <v>2.866292319936528</v>
       </c>
       <c r="U60">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1672940620548227</v>
+        <v>0.120231663343202</v>
       </c>
       <c r="W60">
-        <v>0.122241231690352</v>
+        <v>0.176657482000685</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8121070973535083</v>
+        <v>0.5836488511805922</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6494,22 +6494,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1738912019362374</v>
+        <v>0.1754412019362374</v>
       </c>
       <c r="C61">
-        <v>-13.83450840344358</v>
+        <v>-15.03713691993268</v>
       </c>
       <c r="D61">
-        <v>32.08649159655642</v>
+        <v>31.70286308006732</v>
       </c>
       <c r="E61">
-        <v>29.221</v>
+        <v>30.04</v>
       </c>
       <c r="F61">
-        <v>48.321</v>
+        <v>49.14</v>
       </c>
       <c r="G61">
         <v>2.4</v>
@@ -6530,37 +6530,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M61">
-        <v>9.702856799999999</v>
+        <v>9.867312</v>
       </c>
       <c r="N61">
-        <v>-4.039795575510203</v>
+        <v>-4.204250775510204</v>
       </c>
       <c r="O61">
-        <v>-0.8321978885551019</v>
+        <v>-0.866075659755102</v>
       </c>
       <c r="P61">
-        <v>-3.207597686955101</v>
+        <v>-3.338175115755102</v>
       </c>
       <c r="Q61">
-        <v>-0.2175976869551008</v>
+        <v>-0.3481751157551014</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1699104574532516</v>
+        <v>0.173013218889583</v>
       </c>
       <c r="T61">
-        <v>2.866292319936528</v>
+        <v>2.937949627934941</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.120231663343202</v>
+        <v>0.118227802287482</v>
       </c>
       <c r="W61">
-        <v>0.176657482000685</v>
+        <v>0.1770598573006736</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5836488511805922</v>
+        <v>0.5739213703275823</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1754412019362374</v>
+        <v>0.1769912019362374</v>
       </c>
       <c r="C62">
-        <v>-15.03713691993268</v>
+        <v>-16.230700435236</v>
       </c>
       <c r="D62">
-        <v>31.70286308006732</v>
+        <v>31.32829956476401</v>
       </c>
       <c r="E62">
-        <v>30.04</v>
+        <v>30.859</v>
       </c>
       <c r="F62">
-        <v>49.14</v>
+        <v>49.959</v>
       </c>
       <c r="G62">
         <v>2.4</v>
@@ -6612,37 +6612,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M62">
-        <v>9.867312</v>
+        <v>10.0317672</v>
       </c>
       <c r="N62">
-        <v>-4.204250775510204</v>
+        <v>-4.368705975510204</v>
       </c>
       <c r="O62">
-        <v>-0.866075659755102</v>
+        <v>-0.8999534309551022</v>
       </c>
       <c r="P62">
-        <v>-3.338175115755102</v>
+        <v>-3.468752544555102</v>
       </c>
       <c r="Q62">
-        <v>-0.3481751157551014</v>
+        <v>-0.478752544555102</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.173013218889583</v>
+        <v>0.1762750962970082</v>
       </c>
       <c r="T62">
-        <v>2.937949627934941</v>
+        <v>3.013281669676863</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.118227802287482</v>
+        <v>0.1162896415942445</v>
       </c>
       <c r="W62">
-        <v>0.1770598573006736</v>
+        <v>0.1774490399678757</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5739213703275823</v>
+        <v>0.5645128232730316</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1769912019362374</v>
+        <v>0.1785412019362373</v>
       </c>
       <c r="C63">
-        <v>-16.230700435236</v>
+        <v>-17.41551650151442</v>
       </c>
       <c r="D63">
-        <v>31.32829956476401</v>
+        <v>30.96248349848559</v>
       </c>
       <c r="E63">
-        <v>30.859</v>
+        <v>31.678</v>
       </c>
       <c r="F63">
-        <v>49.959</v>
+        <v>50.77800000000001</v>
       </c>
       <c r="G63">
         <v>2.4</v>
@@ -6694,37 +6694,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M63">
-        <v>10.0317672</v>
+        <v>10.1962224</v>
       </c>
       <c r="N63">
-        <v>-4.368705975510204</v>
+        <v>-4.533161175510205</v>
       </c>
       <c r="O63">
-        <v>-0.8999534309551022</v>
+        <v>-0.9338312021551024</v>
       </c>
       <c r="P63">
-        <v>-3.468752544555102</v>
+        <v>-3.599329973355103</v>
       </c>
       <c r="Q63">
-        <v>-0.478752544555102</v>
+        <v>-0.6093299733551025</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1762750962970082</v>
+        <v>0.1797086514627189</v>
       </c>
       <c r="T63">
-        <v>3.013281669676863</v>
+        <v>3.092578555720991</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1162896415942445</v>
+        <v>0.1144140022136922</v>
       </c>
       <c r="W63">
-        <v>0.1774490399678757</v>
+        <v>0.1778256683554906</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5645128232730316</v>
+        <v>0.5554077777363698</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1785412019362373</v>
+        <v>0.1800912019362373</v>
       </c>
       <c r="C64">
-        <v>-17.41551650151442</v>
+        <v>-18.59188801007713</v>
       </c>
       <c r="D64">
-        <v>30.96248349848559</v>
+        <v>30.60511198992288</v>
       </c>
       <c r="E64">
-        <v>31.678</v>
+        <v>32.497</v>
       </c>
       <c r="F64">
-        <v>50.77800000000001</v>
+        <v>51.597</v>
       </c>
       <c r="G64">
         <v>2.4</v>
@@ -6776,37 +6776,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M64">
-        <v>10.1962224</v>
+        <v>10.3606776</v>
       </c>
       <c r="N64">
-        <v>-4.533161175510205</v>
+        <v>-4.697616375510204</v>
       </c>
       <c r="O64">
-        <v>-0.9338312021551024</v>
+        <v>-0.9677089733551022</v>
       </c>
       <c r="P64">
-        <v>-3.599329973355103</v>
+        <v>-3.729907402155102</v>
       </c>
       <c r="Q64">
-        <v>-0.6093299733551025</v>
+        <v>-0.7399074021551018</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1797086514627189</v>
+        <v>0.1833278042049546</v>
       </c>
       <c r="T64">
-        <v>3.092578555720991</v>
+        <v>3.176161759929666</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1144140022136922</v>
+        <v>0.112597906940459</v>
       </c>
       <c r="W64">
-        <v>0.1778256683554906</v>
+        <v>0.1781903402863558</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5554077777363698</v>
+        <v>0.546591781264364</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6822,22 +6822,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1800912019362373</v>
+        <v>0.1816412019362373</v>
       </c>
       <c r="C65">
-        <v>-18.59188801007713</v>
+        <v>-19.76010402781118</v>
       </c>
       <c r="D65">
-        <v>30.60511198992288</v>
+        <v>30.25589597218882</v>
       </c>
       <c r="E65">
-        <v>32.497</v>
+        <v>33.316</v>
       </c>
       <c r="F65">
-        <v>51.597</v>
+        <v>52.416</v>
       </c>
       <c r="G65">
         <v>2.4</v>
@@ -6858,37 +6858,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M65">
-        <v>10.3606776</v>
+        <v>10.5251328</v>
       </c>
       <c r="N65">
-        <v>-4.697616375510204</v>
+        <v>-4.862071575510205</v>
       </c>
       <c r="O65">
-        <v>-0.9677089733551022</v>
+        <v>-1.001586744555102</v>
       </c>
       <c r="P65">
-        <v>-3.729907402155102</v>
+        <v>-3.860484830955103</v>
       </c>
       <c r="Q65">
-        <v>-0.7399074021551018</v>
+        <v>-0.8704848309551023</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1833278042049546</v>
+        <v>0.1871480209884255</v>
       </c>
       <c r="T65">
-        <v>3.176161759929666</v>
+        <v>3.264388475483268</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.112597906940459</v>
+        <v>0.1108385646445143</v>
       </c>
       <c r="W65">
-        <v>0.1781903402863558</v>
+        <v>0.1785436162193815</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.546591781264364</v>
+        <v>0.5380512846821083</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6904,22 +6904,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1816412019362373</v>
+        <v>0.1831912019362374</v>
       </c>
       <c r="C66">
-        <v>-19.76010402781118</v>
+        <v>-20.92044057699326</v>
       </c>
       <c r="D66">
-        <v>30.25589597218882</v>
+        <v>29.91455942300674</v>
       </c>
       <c r="E66">
-        <v>33.316</v>
+        <v>34.13500000000001</v>
       </c>
       <c r="F66">
-        <v>52.416</v>
+        <v>53.23500000000001</v>
       </c>
       <c r="G66">
         <v>2.4</v>
@@ -6940,37 +6940,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M66">
-        <v>10.5251328</v>
+        <v>10.689588</v>
       </c>
       <c r="N66">
-        <v>-4.862071575510205</v>
+        <v>-5.026526775510206</v>
       </c>
       <c r="O66">
-        <v>-1.001586744555102</v>
+        <v>-1.035464515755103</v>
       </c>
       <c r="P66">
-        <v>-3.860484830955103</v>
+        <v>-3.991062259755103</v>
       </c>
       <c r="Q66">
-        <v>-0.8704848309551023</v>
+        <v>-1.001062259755103</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1871480209884255</v>
+        <v>0.1911865358738091</v>
       </c>
       <c r="T66">
-        <v>3.264388475483268</v>
+        <v>3.357656717639934</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1108385646445143</v>
+        <v>0.1091333559576756</v>
       </c>
       <c r="W66">
-        <v>0.1785436162193815</v>
+        <v>0.1788860221236988</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5380512846821083</v>
+        <v>0.5297735726100758</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6986,22 +6986,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1831912019362374</v>
+        <v>0.1847412019362374</v>
       </c>
       <c r="C67">
-        <v>-20.92044057699326</v>
+        <v>-22.07316136290485</v>
       </c>
       <c r="D67">
-        <v>29.91455942300674</v>
+        <v>29.58083863709516</v>
       </c>
       <c r="E67">
-        <v>34.13500000000001</v>
+        <v>34.95400000000001</v>
       </c>
       <c r="F67">
-        <v>53.23500000000001</v>
+        <v>54.05400000000001</v>
       </c>
       <c r="G67">
         <v>2.4</v>
@@ -7022,37 +7022,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M67">
-        <v>10.689588</v>
+        <v>10.8540432</v>
       </c>
       <c r="N67">
-        <v>-5.026526775510206</v>
+        <v>-5.190981975510205</v>
       </c>
       <c r="O67">
-        <v>-1.035464515755103</v>
+        <v>-1.069342286955102</v>
       </c>
       <c r="P67">
-        <v>-3.991062259755103</v>
+        <v>-4.121639688555103</v>
       </c>
       <c r="Q67">
-        <v>-1.001062259755103</v>
+        <v>-1.131639688555103</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1911865358738091</v>
+        <v>0.1954626104583329</v>
       </c>
       <c r="T67">
-        <v>3.357656717639934</v>
+        <v>3.456411326982284</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1091333559576756</v>
+        <v>0.1074798202613472</v>
       </c>
       <c r="W67">
-        <v>0.1788860221236988</v>
+        <v>0.1792180520915215</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5297735726100758</v>
+        <v>0.521746700297802</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7068,22 +7068,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1847412019362374</v>
+        <v>0.1862912019362374</v>
       </c>
       <c r="C68">
-        <v>-22.07316136290485</v>
+        <v>-23.21851845328198</v>
       </c>
       <c r="D68">
-        <v>29.58083863709516</v>
+        <v>29.25448154671803</v>
       </c>
       <c r="E68">
-        <v>34.95400000000001</v>
+        <v>35.773</v>
       </c>
       <c r="F68">
-        <v>54.05400000000001</v>
+        <v>54.873</v>
       </c>
       <c r="G68">
         <v>2.4</v>
@@ -7104,37 +7104,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M68">
-        <v>10.8540432</v>
+        <v>11.0184984</v>
       </c>
       <c r="N68">
-        <v>-5.190981975510205</v>
+        <v>-5.355437175510206</v>
       </c>
       <c r="O68">
-        <v>-1.069342286955102</v>
+        <v>-1.103220058155102</v>
       </c>
       <c r="P68">
-        <v>-4.121639688555103</v>
+        <v>-4.252217117355103</v>
       </c>
       <c r="Q68">
-        <v>-1.131639688555103</v>
+        <v>-1.262217117355103</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1954626104583329</v>
+        <v>0.1999978410782824</v>
       </c>
       <c r="T68">
-        <v>3.456411326982284</v>
+        <v>3.561151064163566</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1074798202613472</v>
+        <v>0.1058756438395361</v>
       </c>
       <c r="W68">
-        <v>0.1792180520915215</v>
+        <v>0.1795401707170212</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.521746700297802</v>
+        <v>0.5139594361142527</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7150,22 +7150,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1862912019362374</v>
+        <v>0.1878412019362374</v>
       </c>
       <c r="C69">
-        <v>-23.21851845328198</v>
+        <v>-24.3567529132788</v>
       </c>
       <c r="D69">
-        <v>29.25448154671803</v>
+        <v>28.93524708672121</v>
       </c>
       <c r="E69">
-        <v>35.773</v>
+        <v>36.59200000000001</v>
       </c>
       <c r="F69">
-        <v>54.873</v>
+        <v>55.69200000000001</v>
       </c>
       <c r="G69">
         <v>2.4</v>
@@ -7186,37 +7186,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M69">
-        <v>11.0184984</v>
+        <v>11.1829536</v>
       </c>
       <c r="N69">
-        <v>-5.355437175510206</v>
+        <v>-5.519892375510205</v>
       </c>
       <c r="O69">
-        <v>-1.103220058155102</v>
+        <v>-1.137097829355102</v>
       </c>
       <c r="P69">
-        <v>-4.252217117355103</v>
+        <v>-4.382794546155102</v>
       </c>
       <c r="Q69">
-        <v>-1.262217117355103</v>
+        <v>-1.392794546155102</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1999978410782824</v>
+        <v>0.2048165236119787</v>
       </c>
       <c r="T69">
-        <v>3.561151064163566</v>
+        <v>3.672437034918678</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1058756438395361</v>
+        <v>0.10431864907719</v>
       </c>
       <c r="W69">
-        <v>0.1795401707170212</v>
+        <v>0.1798528152653003</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5139594361142527</v>
+        <v>0.5064012091125725</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7232,22 +7232,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1878412019362374</v>
+        <v>0.2141178914176874</v>
       </c>
       <c r="C70">
-        <v>-24.3567529132788</v>
+        <v>-29.69293463628432</v>
       </c>
       <c r="D70">
-        <v>28.93524708672121</v>
+        <v>24.41806536371569</v>
       </c>
       <c r="E70">
-        <v>36.59200000000001</v>
+        <v>37.41100000000001</v>
       </c>
       <c r="F70">
-        <v>55.69200000000001</v>
+        <v>56.51100000000001</v>
       </c>
       <c r="G70">
         <v>2.4</v>
@@ -7268,45 +7268,45 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M70">
-        <v>11.1829536</v>
+        <v>13.3252938</v>
       </c>
       <c r="N70">
-        <v>-5.519892375510205</v>
+        <v>-7.662232575510206</v>
       </c>
       <c r="O70">
-        <v>-1.137097829355102</v>
+        <v>-1.578419910555103</v>
       </c>
       <c r="P70">
-        <v>-4.382794546155102</v>
+        <v>-6.083812664955103</v>
       </c>
       <c r="Q70">
-        <v>-1.392794546155102</v>
+        <v>-3.093812664955103</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2048165236119787</v>
+        <v>0.2118063775396234</v>
       </c>
       <c r="T70">
-        <v>3.672437034918678</v>
+        <v>3.833865532092918</v>
       </c>
       <c r="U70">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.10431864907719</v>
+        <v>0.08754708374571808</v>
       </c>
       <c r="W70">
-        <v>0.1798528152653003</v>
+        <v>0.2151563976527597</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5064012091125725</v>
+        <v>0.4249858434258159</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7314,22 +7314,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2141178914176874</v>
+        <v>0.2160178914176874</v>
       </c>
       <c r="C71">
-        <v>-29.69293463628432</v>
+        <v>-30.78449308360532</v>
       </c>
       <c r="D71">
-        <v>24.41806536371569</v>
+        <v>24.14550691639469</v>
       </c>
       <c r="E71">
-        <v>37.41100000000001</v>
+        <v>38.23000000000001</v>
       </c>
       <c r="F71">
-        <v>56.51100000000001</v>
+        <v>57.33000000000001</v>
       </c>
       <c r="G71">
         <v>2.4</v>
@@ -7350,37 +7350,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M71">
-        <v>13.3252938</v>
+        <v>13.518414</v>
       </c>
       <c r="N71">
-        <v>-7.662232575510206</v>
+        <v>-7.855352775510207</v>
       </c>
       <c r="O71">
-        <v>-1.578419910555103</v>
+        <v>-1.618202671755103</v>
       </c>
       <c r="P71">
-        <v>-6.083812664955103</v>
+        <v>-6.237150103755104</v>
       </c>
       <c r="Q71">
-        <v>-3.093812664955103</v>
+        <v>-3.247150103755104</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2118063775396234</v>
+        <v>0.2173399234576108</v>
       </c>
       <c r="T71">
-        <v>3.833865532092918</v>
+        <v>3.961661049829348</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08754708374571808</v>
+        <v>0.08629641112077924</v>
       </c>
       <c r="W71">
-        <v>0.2151563976527597</v>
+        <v>0.2154513062577203</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4249858434258159</v>
+        <v>0.4189146170911614</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7396,22 +7396,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2160178914176874</v>
+        <v>0.2179178914176874</v>
       </c>
       <c r="C72">
-        <v>-30.78449308360532</v>
+        <v>-31.87003401530788</v>
       </c>
       <c r="D72">
-        <v>24.14550691639469</v>
+        <v>23.87896598469213</v>
       </c>
       <c r="E72">
-        <v>38.23000000000001</v>
+        <v>39.04900000000001</v>
       </c>
       <c r="F72">
-        <v>57.33000000000001</v>
+        <v>58.14900000000001</v>
       </c>
       <c r="G72">
         <v>2.4</v>
@@ -7432,37 +7432,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M72">
-        <v>13.518414</v>
+        <v>13.7115342</v>
       </c>
       <c r="N72">
-        <v>-7.855352775510207</v>
+        <v>-8.048472975510206</v>
       </c>
       <c r="O72">
-        <v>-1.618202671755103</v>
+        <v>-1.657985432955103</v>
       </c>
       <c r="P72">
-        <v>-6.237150103755104</v>
+        <v>-6.390487542555103</v>
       </c>
       <c r="Q72">
-        <v>-3.247150103755104</v>
+        <v>-3.400487542555103</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2173399234576108</v>
+        <v>0.2232550932320112</v>
       </c>
       <c r="T72">
-        <v>3.961661049829348</v>
+        <v>4.098270051547602</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08629641112077924</v>
+        <v>0.08508096871062744</v>
       </c>
       <c r="W72">
-        <v>0.2154513062577203</v>
+        <v>0.2157379075780341</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4189146170911614</v>
+        <v>0.413014411216638</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7478,22 +7478,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2179178914176874</v>
+        <v>0.2198178914176874</v>
       </c>
       <c r="C73">
-        <v>-31.87003401530787</v>
+        <v>-32.94975453663642</v>
       </c>
       <c r="D73">
-        <v>23.87896598469213</v>
+        <v>23.61824546336358</v>
       </c>
       <c r="E73">
-        <v>39.049</v>
+        <v>39.868</v>
       </c>
       <c r="F73">
-        <v>58.149</v>
+        <v>58.968</v>
       </c>
       <c r="G73">
         <v>2.4</v>
@@ -7514,37 +7514,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M73">
-        <v>13.7115342</v>
+        <v>13.9046544</v>
       </c>
       <c r="N73">
-        <v>-8.048472975510204</v>
+        <v>-8.241593175510205</v>
       </c>
       <c r="O73">
-        <v>-1.657985432955102</v>
+        <v>-1.697768194155102</v>
       </c>
       <c r="P73">
-        <v>-6.390487542555102</v>
+        <v>-6.543824981355103</v>
       </c>
       <c r="Q73">
-        <v>-3.400487542555102</v>
+        <v>-3.553824981355103</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2232550932320111</v>
+        <v>0.2295927751331544</v>
       </c>
       <c r="T73">
-        <v>4.0982700515476</v>
+        <v>4.244636839102872</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08508096871062744</v>
+        <v>0.0838992885896465</v>
       </c>
       <c r="W73">
-        <v>0.2157379075780341</v>
+        <v>0.2160165477505614</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4130144112166381</v>
+        <v>0.4072780999497403</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7560,22 +7560,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2198178914176874</v>
+        <v>0.2217178914176874</v>
       </c>
       <c r="C74">
-        <v>-32.94975453663642</v>
+        <v>-34.02384323749996</v>
       </c>
       <c r="D74">
-        <v>23.61824546336358</v>
+        <v>23.36315676250005</v>
       </c>
       <c r="E74">
-        <v>39.868</v>
+        <v>40.687</v>
       </c>
       <c r="F74">
-        <v>58.968</v>
+        <v>59.78700000000001</v>
       </c>
       <c r="G74">
         <v>2.4</v>
@@ -7596,37 +7596,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M74">
-        <v>13.9046544</v>
+        <v>14.0977746</v>
       </c>
       <c r="N74">
-        <v>-8.241593175510205</v>
+        <v>-8.434713375510206</v>
       </c>
       <c r="O74">
-        <v>-1.697768194155102</v>
+        <v>-1.737550955355103</v>
       </c>
       <c r="P74">
-        <v>-6.543824981355103</v>
+        <v>-6.697162420155104</v>
       </c>
       <c r="Q74">
-        <v>-3.553824981355103</v>
+        <v>-3.707162420155104</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2295927751331544</v>
+        <v>0.2363999149529008</v>
       </c>
       <c r="T74">
-        <v>4.244636839102872</v>
+        <v>4.401845610921496</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0838992885896465</v>
+        <v>0.08274998326650065</v>
       </c>
       <c r="W74">
-        <v>0.2160165477505614</v>
+        <v>0.2162875539457592</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4072780999497403</v>
+        <v>0.4016989478956342</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7642,22 +7642,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2217178914176874</v>
+        <v>0.2236178914176874</v>
       </c>
       <c r="C75">
-        <v>-34.02384323749996</v>
+        <v>-35.0924806474076</v>
       </c>
       <c r="D75">
-        <v>23.36315676250005</v>
+        <v>23.1135193525924</v>
       </c>
       <c r="E75">
-        <v>40.687</v>
+        <v>41.506</v>
       </c>
       <c r="F75">
-        <v>59.78700000000001</v>
+        <v>60.606</v>
       </c>
       <c r="G75">
         <v>2.4</v>
@@ -7678,37 +7678,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M75">
-        <v>14.0977746</v>
+        <v>14.2908948</v>
       </c>
       <c r="N75">
-        <v>-8.434713375510206</v>
+        <v>-8.627833575510204</v>
       </c>
       <c r="O75">
-        <v>-1.737550955355103</v>
+        <v>-1.777333716555102</v>
       </c>
       <c r="P75">
-        <v>-6.697162420155104</v>
+        <v>-6.850499858955102</v>
       </c>
       <c r="Q75">
-        <v>-3.707162420155104</v>
+        <v>-3.860499858955102</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2363999149529008</v>
+        <v>0.2437306809126278</v>
       </c>
       <c r="T75">
-        <v>4.401845610921496</v>
+        <v>4.571147365187708</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08274998326650065</v>
+        <v>0.08163174024938578</v>
       </c>
       <c r="W75">
-        <v>0.2162875539457592</v>
+        <v>0.2165512356491948</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4016989478956342</v>
+        <v>0.3962705837348824</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7724,22 +7724,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2236178914176874</v>
+        <v>0.2255178914176874</v>
       </c>
       <c r="C76">
-        <v>-35.0924806474076</v>
+        <v>-36.15583966154638</v>
       </c>
       <c r="D76">
-        <v>23.1135193525924</v>
+        <v>22.86916033845363</v>
       </c>
       <c r="E76">
-        <v>41.506</v>
+        <v>42.325</v>
       </c>
       <c r="F76">
-        <v>60.606</v>
+        <v>61.425</v>
       </c>
       <c r="G76">
         <v>2.4</v>
@@ -7760,37 +7760,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M76">
-        <v>14.2908948</v>
+        <v>14.484015</v>
       </c>
       <c r="N76">
-        <v>-8.627833575510204</v>
+        <v>-8.820953775510205</v>
       </c>
       <c r="O76">
-        <v>-1.777333716555102</v>
+        <v>-1.817116477755102</v>
       </c>
       <c r="P76">
-        <v>-6.850499858955102</v>
+        <v>-7.003837297755102</v>
       </c>
       <c r="Q76">
-        <v>-3.860499858955102</v>
+        <v>-4.013837297755102</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2437306809126278</v>
+        <v>0.2516479081491328</v>
       </c>
       <c r="T76">
-        <v>4.571147365187708</v>
+        <v>4.753993259795217</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08163174024938578</v>
+        <v>0.08054331704606064</v>
       </c>
       <c r="W76">
-        <v>0.2165512356491948</v>
+        <v>0.2168078858405389</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3962705837348824</v>
+        <v>0.3909869759517507</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7806,22 +7806,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2255178914176874</v>
+        <v>0.2274178914176874</v>
       </c>
       <c r="C77">
-        <v>-36.15583966154638</v>
+        <v>-37.21408594011444</v>
       </c>
       <c r="D77">
-        <v>22.86916033845363</v>
+        <v>22.62991405988556</v>
       </c>
       <c r="E77">
-        <v>42.325</v>
+        <v>43.14400000000001</v>
       </c>
       <c r="F77">
-        <v>61.425</v>
+        <v>62.24400000000001</v>
       </c>
       <c r="G77">
         <v>2.4</v>
@@ -7842,37 +7842,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M77">
-        <v>14.484015</v>
+        <v>14.6771352</v>
       </c>
       <c r="N77">
-        <v>-8.820953775510205</v>
+        <v>-9.014073975510206</v>
       </c>
       <c r="O77">
-        <v>-1.817116477755102</v>
+        <v>-1.856899238955102</v>
       </c>
       <c r="P77">
-        <v>-7.003837297755102</v>
+        <v>-7.157174736555104</v>
       </c>
       <c r="Q77">
-        <v>-4.013837297755102</v>
+        <v>-4.167174736555103</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2516479081491328</v>
+        <v>0.2602249043220134</v>
       </c>
       <c r="T77">
-        <v>4.753993259795217</v>
+        <v>4.952076312286684</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08054331704606064</v>
+        <v>0.07948353655861247</v>
       </c>
       <c r="W77">
-        <v>0.2168078858405389</v>
+        <v>0.2170577820794792</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3909869759517507</v>
+        <v>0.3858424104787013</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2274178914176874</v>
+        <v>0.2293178914176874</v>
       </c>
       <c r="C78">
-        <v>-37.21408594011444</v>
+        <v>-38.26737828284806</v>
       </c>
       <c r="D78">
-        <v>22.62991405988556</v>
+        <v>22.39562171715194</v>
       </c>
       <c r="E78">
-        <v>43.14400000000001</v>
+        <v>43.963</v>
       </c>
       <c r="F78">
-        <v>62.24400000000001</v>
+        <v>63.063</v>
       </c>
       <c r="G78">
         <v>2.4</v>
@@ -7924,37 +7924,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M78">
-        <v>14.6771352</v>
+        <v>14.8702554</v>
       </c>
       <c r="N78">
-        <v>-9.014073975510206</v>
+        <v>-9.207194175510205</v>
       </c>
       <c r="O78">
-        <v>-1.856899238955102</v>
+        <v>-1.896682000155102</v>
       </c>
       <c r="P78">
-        <v>-7.157174736555104</v>
+        <v>-7.310512175355102</v>
       </c>
       <c r="Q78">
-        <v>-4.167174736555103</v>
+        <v>-4.320512175355102</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2602249043220134</v>
+        <v>0.2695477262490575</v>
       </c>
       <c r="T78">
-        <v>4.952076312286684</v>
+        <v>5.167383978038279</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07948353655861247</v>
+        <v>0.07845128283707206</v>
       </c>
       <c r="W78">
-        <v>0.2170577820794792</v>
+        <v>0.2173011875070184</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3858424104787013</v>
+        <v>0.380831470082874</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7970,22 +7970,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2293178914176874</v>
+        <v>0.2312178914176874</v>
       </c>
       <c r="C79">
-        <v>-38.26737828284806</v>
+        <v>-39.31586898052154</v>
       </c>
       <c r="D79">
-        <v>22.39562171715194</v>
+        <v>22.16613101947847</v>
       </c>
       <c r="E79">
-        <v>43.963</v>
+        <v>44.782</v>
       </c>
       <c r="F79">
-        <v>63.063</v>
+        <v>63.88200000000001</v>
       </c>
       <c r="G79">
         <v>2.4</v>
@@ -8006,37 +8006,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M79">
-        <v>14.8702554</v>
+        <v>15.0633756</v>
       </c>
       <c r="N79">
-        <v>-9.207194175510205</v>
+        <v>-9.400314375510206</v>
       </c>
       <c r="O79">
-        <v>-1.896682000155102</v>
+        <v>-1.936464761355102</v>
       </c>
       <c r="P79">
-        <v>-7.310512175355102</v>
+        <v>-7.463849614155103</v>
       </c>
       <c r="Q79">
-        <v>-4.320512175355102</v>
+        <v>-4.473849614155103</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2695477262490575</v>
+        <v>0.2797180774421965</v>
       </c>
       <c r="T79">
-        <v>5.167383978038279</v>
+        <v>5.402265067949111</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07845128283707206</v>
+        <v>0.07744549715967369</v>
       </c>
       <c r="W79">
-        <v>0.2173011875070184</v>
+        <v>0.217538351769749</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.380831470082874</v>
+        <v>0.3759490153382218</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2312178914176874</v>
+        <v>0.2331178914176874</v>
       </c>
       <c r="C80">
-        <v>-39.31586898052154</v>
+        <v>-40.35970414505528</v>
       </c>
       <c r="D80">
-        <v>22.16613101947847</v>
+        <v>21.94129585494473</v>
       </c>
       <c r="E80">
-        <v>44.782</v>
+        <v>45.60100000000001</v>
       </c>
       <c r="F80">
-        <v>63.88200000000001</v>
+        <v>64.70100000000001</v>
       </c>
       <c r="G80">
         <v>2.4</v>
@@ -8088,37 +8088,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M80">
-        <v>15.0633756</v>
+        <v>15.2564958</v>
       </c>
       <c r="N80">
-        <v>-9.400314375510206</v>
+        <v>-9.593434575510207</v>
       </c>
       <c r="O80">
-        <v>-1.936464761355102</v>
+        <v>-1.976247522555103</v>
       </c>
       <c r="P80">
-        <v>-7.463849614155103</v>
+        <v>-7.617187052955104</v>
       </c>
       <c r="Q80">
-        <v>-4.473849614155103</v>
+        <v>-4.627187052955104</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2797180774421965</v>
+        <v>0.2908570335108725</v>
       </c>
       <c r="T80">
-        <v>5.402265067949111</v>
+        <v>5.659515785470497</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07744549715967369</v>
+        <v>0.07646517441081706</v>
       </c>
       <c r="W80">
-        <v>0.217538351769749</v>
+        <v>0.2177695118739293</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3759490153382218</v>
+        <v>0.3711901670428012</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8134,22 +8134,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2331178914176874</v>
+        <v>0.2350178914176874</v>
       </c>
       <c r="C81">
-        <v>-40.35970414505528</v>
+        <v>-41.39902401973547</v>
       </c>
       <c r="D81">
-        <v>21.94129585494473</v>
+        <v>21.72097598026454</v>
       </c>
       <c r="E81">
-        <v>45.60100000000001</v>
+        <v>46.42000000000001</v>
       </c>
       <c r="F81">
-        <v>64.70100000000001</v>
+        <v>65.52000000000001</v>
       </c>
       <c r="G81">
         <v>2.4</v>
@@ -8170,37 +8170,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M81">
-        <v>15.2564958</v>
+        <v>15.449616</v>
       </c>
       <c r="N81">
-        <v>-9.593434575510207</v>
+        <v>-9.786554775510206</v>
       </c>
       <c r="O81">
-        <v>-1.976247522555103</v>
+        <v>-2.016030283755103</v>
       </c>
       <c r="P81">
-        <v>-7.617187052955104</v>
+        <v>-7.770524491755103</v>
       </c>
       <c r="Q81">
-        <v>-4.627187052955104</v>
+        <v>-4.780524491755103</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2908570335108725</v>
+        <v>0.3031098851864162</v>
       </c>
       <c r="T81">
-        <v>5.659515785470497</v>
+        <v>5.942491574744023</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07646517441081706</v>
+        <v>0.07550935973068185</v>
       </c>
       <c r="W81">
-        <v>0.2177695118739293</v>
+        <v>0.2179948929755052</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3711901670428012</v>
+        <v>0.3665502899547662</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8216,22 +8216,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2350178914176874</v>
+        <v>0.2369178914176874</v>
       </c>
       <c r="C82">
-        <v>-41.39902401973547</v>
+        <v>-42.43396327092942</v>
       </c>
       <c r="D82">
-        <v>21.72097598026454</v>
+        <v>21.50503672907059</v>
       </c>
       <c r="E82">
-        <v>46.42000000000001</v>
+        <v>47.23900000000001</v>
       </c>
       <c r="F82">
-        <v>65.52000000000001</v>
+        <v>66.33900000000001</v>
       </c>
       <c r="G82">
         <v>2.4</v>
@@ -8252,37 +8252,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M82">
-        <v>15.449616</v>
+        <v>15.6427362</v>
       </c>
       <c r="N82">
-        <v>-9.786554775510206</v>
+        <v>-9.979674975510207</v>
       </c>
       <c r="O82">
-        <v>-2.016030283755103</v>
+        <v>-2.055813044955103</v>
       </c>
       <c r="P82">
-        <v>-7.770524491755103</v>
+        <v>-7.923861930555104</v>
       </c>
       <c r="Q82">
-        <v>-4.780524491755103</v>
+        <v>-4.933861930555103</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3031098851864162</v>
+        <v>0.3166525107225433</v>
       </c>
       <c r="T82">
-        <v>5.942491574744023</v>
+        <v>6.255254289204234</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07550935973068185</v>
+        <v>0.0745771454130191</v>
       </c>
       <c r="W82">
-        <v>0.2179948929755052</v>
+        <v>0.2182147091116101</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3665502899547662</v>
+        <v>0.3620249777331024</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8298,22 +8298,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2369178914176874</v>
+        <v>0.2388178914176874</v>
       </c>
       <c r="C83">
-        <v>-42.43396327092942</v>
+        <v>-43.46465126257169</v>
       </c>
       <c r="D83">
-        <v>21.50503672907059</v>
+        <v>21.29334873742832</v>
       </c>
       <c r="E83">
-        <v>47.23900000000001</v>
+        <v>48.05800000000001</v>
       </c>
       <c r="F83">
-        <v>66.33900000000001</v>
+        <v>67.15800000000002</v>
       </c>
       <c r="G83">
         <v>2.4</v>
@@ -8334,37 +8334,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M83">
-        <v>15.6427362</v>
+        <v>15.8358564</v>
       </c>
       <c r="N83">
-        <v>-9.979674975510207</v>
+        <v>-10.17279517551021</v>
       </c>
       <c r="O83">
-        <v>-2.055813044955103</v>
+        <v>-2.095595806155103</v>
       </c>
       <c r="P83">
-        <v>-7.923861930555104</v>
+        <v>-8.077199369355105</v>
       </c>
       <c r="Q83">
-        <v>-4.933861930555103</v>
+        <v>-5.087199369355105</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3166525107225433</v>
+        <v>0.3316998724293513</v>
       </c>
       <c r="T83">
-        <v>6.255254289204234</v>
+        <v>6.602768416382247</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0745771454130191</v>
+        <v>0.07366766802993349</v>
       </c>
       <c r="W83">
-        <v>0.2182147091116101</v>
+        <v>0.2184291638785417</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3620249777331024</v>
+        <v>0.3576100389802597</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8380,22 +8380,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2388178914176874</v>
+        <v>0.2407178914176874</v>
       </c>
       <c r="C84">
-        <v>-43.46465126257169</v>
+        <v>-44.4912123145965</v>
       </c>
       <c r="D84">
-        <v>21.29334873742832</v>
+        <v>21.08578768540351</v>
       </c>
       <c r="E84">
-        <v>48.05800000000001</v>
+        <v>48.877</v>
       </c>
       <c r="F84">
-        <v>67.15800000000002</v>
+        <v>67.977</v>
       </c>
       <c r="G84">
         <v>2.4</v>
@@ -8416,37 +8416,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M84">
-        <v>15.8358564</v>
+        <v>16.0289766</v>
       </c>
       <c r="N84">
-        <v>-10.17279517551021</v>
+        <v>-10.3659153755102</v>
       </c>
       <c r="O84">
-        <v>-2.095595806155103</v>
+        <v>-2.135378567355102</v>
       </c>
       <c r="P84">
-        <v>-8.077199369355105</v>
+        <v>-8.230536808155101</v>
       </c>
       <c r="Q84">
-        <v>-5.087199369355105</v>
+        <v>-5.240536808155101</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3316998724293513</v>
+        <v>0.348517511984019</v>
       </c>
       <c r="T84">
-        <v>6.602768416382247</v>
+        <v>6.99116655852238</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07366766802993349</v>
+        <v>0.07278010576451263</v>
       </c>
       <c r="W84">
-        <v>0.2184291638785417</v>
+        <v>0.2186384510607279</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3576100389802597</v>
+        <v>0.3533014842937506</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8462,22 +8462,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2407178914176874</v>
+        <v>0.2426178914176874</v>
       </c>
       <c r="C85">
-        <v>-44.4912123145965</v>
+        <v>-45.51376594640148</v>
       </c>
       <c r="D85">
-        <v>21.08578768540351</v>
+        <v>20.88223405359853</v>
       </c>
       <c r="E85">
-        <v>48.877</v>
+        <v>49.69600000000001</v>
       </c>
       <c r="F85">
-        <v>67.977</v>
+        <v>68.79600000000001</v>
       </c>
       <c r="G85">
         <v>2.4</v>
@@ -8498,37 +8498,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M85">
-        <v>16.0289766</v>
+        <v>16.2220968</v>
       </c>
       <c r="N85">
-        <v>-10.3659153755102</v>
+        <v>-10.55903557551021</v>
       </c>
       <c r="O85">
-        <v>-2.135378567355102</v>
+        <v>-2.175161328555103</v>
       </c>
       <c r="P85">
-        <v>-8.230536808155101</v>
+        <v>-8.383874246955104</v>
       </c>
       <c r="Q85">
-        <v>-5.240536808155101</v>
+        <v>-5.393874246955104</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.348517511984019</v>
+        <v>0.3674373564830203</v>
       </c>
       <c r="T85">
-        <v>6.99116655852238</v>
+        <v>7.428114468430032</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07278010576451263</v>
+        <v>0.07191367593398272</v>
       </c>
       <c r="W85">
-        <v>0.2186384510607279</v>
+        <v>0.2188427552147669</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3533014842937506</v>
+        <v>0.3490955142426345</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8544,22 +8544,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2426178914176874</v>
+        <v>0.2445178914176874</v>
       </c>
       <c r="C86">
-        <v>-45.51376594640148</v>
+        <v>-46.53242710634424</v>
       </c>
       <c r="D86">
-        <v>20.88223405359853</v>
+        <v>20.68257289365577</v>
       </c>
       <c r="E86">
-        <v>49.69600000000001</v>
+        <v>50.51500000000001</v>
       </c>
       <c r="F86">
-        <v>68.79600000000001</v>
+        <v>69.61500000000001</v>
       </c>
       <c r="G86">
         <v>2.4</v>
@@ -8580,37 +8580,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M86">
-        <v>16.2220968</v>
+        <v>16.415217</v>
       </c>
       <c r="N86">
-        <v>-10.55903557551021</v>
+        <v>-10.75215577551021</v>
       </c>
       <c r="O86">
-        <v>-2.175161328555103</v>
+        <v>-2.214944089755102</v>
       </c>
       <c r="P86">
-        <v>-8.383874246955104</v>
+        <v>-8.537211685755103</v>
       </c>
       <c r="Q86">
-        <v>-5.393874246955104</v>
+        <v>-5.547211685755103</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3674373564830201</v>
+        <v>0.3888798469152214</v>
       </c>
       <c r="T86">
-        <v>7.428114468430025</v>
+        <v>7.923322099658693</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07191367593398272</v>
+        <v>0.07106763268770055</v>
       </c>
       <c r="W86">
-        <v>0.2188427552147669</v>
+        <v>0.2190422522122402</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3490955142426345</v>
+        <v>0.3449885081927212</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8626,22 +8626,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2445178914176874</v>
+        <v>0.2464178914176874</v>
       </c>
       <c r="C87">
-        <v>-46.53242710634424</v>
+        <v>-47.54730638819815</v>
       </c>
       <c r="D87">
-        <v>20.68257289365577</v>
+        <v>20.48669361180185</v>
       </c>
       <c r="E87">
-        <v>50.51500000000001</v>
+        <v>51.334</v>
       </c>
       <c r="F87">
-        <v>69.61500000000001</v>
+        <v>70.434</v>
       </c>
       <c r="G87">
         <v>2.4</v>
@@ -8662,37 +8662,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M87">
-        <v>16.415217</v>
+        <v>16.6083372</v>
       </c>
       <c r="N87">
-        <v>-10.75215577551021</v>
+        <v>-10.9452759755102</v>
       </c>
       <c r="O87">
-        <v>-2.214944089755102</v>
+        <v>-2.254726850955102</v>
       </c>
       <c r="P87">
-        <v>-8.537211685755103</v>
+        <v>-8.690549124555103</v>
       </c>
       <c r="Q87">
-        <v>-5.547211685755103</v>
+        <v>-5.700549124555103</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3888798469152214</v>
+        <v>0.4133855502663087</v>
       </c>
       <c r="T87">
-        <v>7.923322099658693</v>
+        <v>8.489273678205743</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07106763268770055</v>
+        <v>0.07024126486575057</v>
       </c>
       <c r="W87">
-        <v>0.2190422522122402</v>
+        <v>0.219237109744656</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3449885081927212</v>
+        <v>0.3409770139114104</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8708,22 +8708,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2464178914176874</v>
+        <v>0.2483178914176874</v>
       </c>
       <c r="C88">
-        <v>-47.54730638819815</v>
+        <v>-48.55851023542341</v>
       </c>
       <c r="D88">
-        <v>20.48669361180185</v>
+        <v>20.29448976457659</v>
       </c>
       <c r="E88">
-        <v>51.334</v>
+        <v>52.153</v>
       </c>
       <c r="F88">
-        <v>70.434</v>
+        <v>71.253</v>
       </c>
       <c r="G88">
         <v>2.4</v>
@@ -8744,37 +8744,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M88">
-        <v>16.6083372</v>
+        <v>16.8014574</v>
       </c>
       <c r="N88">
-        <v>-10.9452759755102</v>
+        <v>-11.1383961755102</v>
       </c>
       <c r="O88">
-        <v>-2.254726850955102</v>
+        <v>-2.294509612155102</v>
       </c>
       <c r="P88">
-        <v>-8.690549124555103</v>
+        <v>-8.843886563355102</v>
       </c>
       <c r="Q88">
-        <v>-5.700549124555103</v>
+        <v>-5.853886563355102</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4133855502663087</v>
+        <v>0.4416613618252556</v>
       </c>
       <c r="T88">
-        <v>8.489273678205743</v>
+        <v>9.142294730375417</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07024126486575057</v>
+        <v>0.06943389400522471</v>
       </c>
       <c r="W88">
-        <v>0.219237109744656</v>
+        <v>0.219427487793568</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3409770139114104</v>
+        <v>0.3370577378894403</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8790,22 +8790,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2483178914176874</v>
+        <v>0.2502178914176874</v>
       </c>
       <c r="C89">
-        <v>-48.55851023542341</v>
+        <v>-49.56614113404621</v>
       </c>
       <c r="D89">
-        <v>20.29448976457659</v>
+        <v>20.1058588659538</v>
       </c>
       <c r="E89">
-        <v>52.153</v>
+        <v>52.972</v>
       </c>
       <c r="F89">
-        <v>71.253</v>
+        <v>72.072</v>
       </c>
       <c r="G89">
         <v>2.4</v>
@@ -8826,37 +8826,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M89">
-        <v>16.8014574</v>
+        <v>16.9945776</v>
       </c>
       <c r="N89">
-        <v>-11.1383961755102</v>
+        <v>-11.33151637551021</v>
       </c>
       <c r="O89">
-        <v>-2.294509612155102</v>
+        <v>-2.334292373355103</v>
       </c>
       <c r="P89">
-        <v>-8.843886563355102</v>
+        <v>-8.997224002155104</v>
       </c>
       <c r="Q89">
-        <v>-5.853886563355102</v>
+        <v>-6.007224002155104</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4416613618252556</v>
+        <v>0.4746498086440268</v>
       </c>
       <c r="T89">
-        <v>9.142294730375417</v>
+        <v>9.904152624573369</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06943389400522471</v>
+        <v>0.06864487248243804</v>
       </c>
       <c r="W89">
-        <v>0.219427487793568</v>
+        <v>0.2196135390686411</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3370577378894403</v>
+        <v>0.3332275363225148</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8872,22 +8872,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2502178914176874</v>
+        <v>0.2521178914176874</v>
       </c>
       <c r="C90">
-        <v>-49.56614113404621</v>
+        <v>-50.57029779488069</v>
       </c>
       <c r="D90">
-        <v>20.1058588659538</v>
+        <v>19.92070220511931</v>
       </c>
       <c r="E90">
-        <v>52.972</v>
+        <v>53.791</v>
       </c>
       <c r="F90">
-        <v>72.072</v>
+        <v>72.89100000000001</v>
       </c>
       <c r="G90">
         <v>2.4</v>
@@ -8908,37 +8908,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M90">
-        <v>16.9945776</v>
+        <v>17.1876978</v>
       </c>
       <c r="N90">
-        <v>-11.33151637551021</v>
+        <v>-11.52463657551021</v>
       </c>
       <c r="O90">
-        <v>-2.334292373355103</v>
+        <v>-2.374075134555103</v>
       </c>
       <c r="P90">
-        <v>-8.997224002155104</v>
+        <v>-9.150561440955103</v>
       </c>
       <c r="Q90">
-        <v>-6.007224002155104</v>
+        <v>-6.160561440955103</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4746498086440268</v>
+        <v>0.513636154884393</v>
       </c>
       <c r="T90">
-        <v>9.904152624573369</v>
+        <v>10.80453013589822</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06864487248243804</v>
+        <v>0.06787358178038819</v>
       </c>
       <c r="W90">
-        <v>0.2196135390686411</v>
+        <v>0.2197954094161845</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3332275363225148</v>
+        <v>0.3294834067009135</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8954,22 +8954,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2521178914176874</v>
+        <v>0.2540178914176874</v>
       </c>
       <c r="C91">
-        <v>-50.57029779488069</v>
+        <v>-51.57107532577405</v>
       </c>
       <c r="D91">
-        <v>19.92070220511931</v>
+        <v>19.73892467422596</v>
       </c>
       <c r="E91">
-        <v>53.791</v>
+        <v>54.61000000000001</v>
       </c>
       <c r="F91">
-        <v>72.89100000000001</v>
+        <v>73.71000000000001</v>
       </c>
       <c r="G91">
         <v>2.4</v>
@@ -8990,37 +8990,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M91">
-        <v>17.1876978</v>
+        <v>17.380818</v>
       </c>
       <c r="N91">
-        <v>-11.52463657551021</v>
+        <v>-11.71775677551021</v>
       </c>
       <c r="O91">
-        <v>-2.374075134555103</v>
+        <v>-2.413857895755102</v>
       </c>
       <c r="P91">
-        <v>-9.150561440955103</v>
+        <v>-9.303898879755103</v>
       </c>
       <c r="Q91">
-        <v>-6.160561440955103</v>
+        <v>-6.313898879755103</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.513636154884393</v>
+        <v>0.5604197703728322</v>
       </c>
       <c r="T91">
-        <v>10.80453013589822</v>
+        <v>11.88498314948804</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06787358178038819</v>
+        <v>0.06711943087171721</v>
       </c>
       <c r="W91">
-        <v>0.2197954094161845</v>
+        <v>0.2199732382004491</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3294834067009135</v>
+        <v>0.3258224799597922</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2540178914176874</v>
+        <v>0.2559178914176874</v>
       </c>
       <c r="C92">
-        <v>-51.57107532577405</v>
+        <v>-52.56856539450635</v>
       </c>
       <c r="D92">
-        <v>19.73892467422596</v>
+        <v>19.56043460549366</v>
       </c>
       <c r="E92">
-        <v>54.61000000000001</v>
+        <v>55.42900000000001</v>
       </c>
       <c r="F92">
-        <v>73.71000000000001</v>
+        <v>74.52900000000001</v>
       </c>
       <c r="G92">
         <v>2.4</v>
@@ -9072,37 +9072,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M92">
-        <v>17.380818</v>
+        <v>17.5739382</v>
       </c>
       <c r="N92">
-        <v>-11.71775677551021</v>
+        <v>-11.91087697551021</v>
       </c>
       <c r="O92">
-        <v>-2.413857895755102</v>
+        <v>-2.453640656955103</v>
       </c>
       <c r="P92">
-        <v>-9.303898879755103</v>
+        <v>-9.457236318555104</v>
       </c>
       <c r="Q92">
-        <v>-6.313898879755103</v>
+        <v>-6.467236318555104</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5604197703728322</v>
+        <v>0.6175997448587025</v>
       </c>
       <c r="T92">
-        <v>11.88498314948804</v>
+        <v>13.20553683276449</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06711943087171721</v>
+        <v>0.06638185470829173</v>
       </c>
       <c r="W92">
-        <v>0.2199732382004491</v>
+        <v>0.2201471586597848</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3258224799597922</v>
+        <v>0.3222420131470473</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9118,22 +9118,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2559178914176874</v>
+        <v>0.2578178914176874</v>
       </c>
       <c r="C93">
-        <v>-52.56856539450635</v>
+        <v>-53.56285638293158</v>
       </c>
       <c r="D93">
-        <v>19.56043460549366</v>
+        <v>19.38514361706844</v>
       </c>
       <c r="E93">
-        <v>55.42900000000001</v>
+        <v>56.24800000000001</v>
       </c>
       <c r="F93">
-        <v>74.52900000000001</v>
+        <v>75.34800000000001</v>
       </c>
       <c r="G93">
         <v>2.4</v>
@@ -9154,37 +9154,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M93">
-        <v>17.5739382</v>
+        <v>17.7670584</v>
       </c>
       <c r="N93">
-        <v>-11.91087697551021</v>
+        <v>-12.10399717551021</v>
       </c>
       <c r="O93">
-        <v>-2.453640656955103</v>
+        <v>-2.493423418155103</v>
       </c>
       <c r="P93">
-        <v>-9.457236318555104</v>
+        <v>-9.610573757355104</v>
       </c>
       <c r="Q93">
-        <v>-6.467236318555104</v>
+        <v>-6.620573757355103</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6175997448587025</v>
+        <v>0.6890747129660406</v>
       </c>
       <c r="T93">
-        <v>13.20553683276449</v>
+        <v>14.85622893686006</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06638185470829173</v>
+        <v>0.06566031280928855</v>
       </c>
       <c r="W93">
-        <v>0.2201471586597848</v>
+        <v>0.2203172982395698</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3222420131470473</v>
+        <v>0.318739382569362</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9200,22 +9200,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2578178914176874</v>
+        <v>0.2597178914176874</v>
       </c>
       <c r="C94">
-        <v>-53.56285638293158</v>
+        <v>-54.55403353290411</v>
       </c>
       <c r="D94">
-        <v>19.38514361706844</v>
+        <v>19.21296646709591</v>
       </c>
       <c r="E94">
-        <v>56.24800000000001</v>
+        <v>57.06700000000001</v>
       </c>
       <c r="F94">
-        <v>75.34800000000001</v>
+        <v>76.16700000000002</v>
       </c>
       <c r="G94">
         <v>2.4</v>
@@ -9236,37 +9236,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M94">
-        <v>17.7670584</v>
+        <v>17.96017860000001</v>
       </c>
       <c r="N94">
-        <v>-12.10399717551021</v>
+        <v>-12.29711737551021</v>
       </c>
       <c r="O94">
-        <v>-2.493423418155103</v>
+        <v>-2.533206179355104</v>
       </c>
       <c r="P94">
-        <v>-9.610573757355104</v>
+        <v>-9.763911196155107</v>
       </c>
       <c r="Q94">
-        <v>-6.620573757355103</v>
+        <v>-6.773911196155106</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6890747129660406</v>
+        <v>0.7809711005326179</v>
       </c>
       <c r="T94">
-        <v>14.85622893686006</v>
+        <v>16.9785473564115</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06566031280928855</v>
+        <v>0.06495428794037147</v>
       </c>
       <c r="W94">
-        <v>0.2203172982395698</v>
+        <v>0.2204837789036604</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.318739382569362</v>
+        <v>0.315312077380444</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9282,22 +9282,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2597178914176874</v>
+        <v>0.2616178914176874</v>
       </c>
       <c r="C95">
-        <v>-54.55403353290411</v>
+        <v>-55.54217908449709</v>
       </c>
       <c r="D95">
-        <v>19.21296646709591</v>
+        <v>19.04382091550291</v>
       </c>
       <c r="E95">
-        <v>57.06700000000001</v>
+        <v>57.886</v>
       </c>
       <c r="F95">
-        <v>76.16700000000002</v>
+        <v>76.986</v>
       </c>
       <c r="G95">
         <v>2.4</v>
@@ -9318,37 +9318,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M95">
-        <v>17.96017860000001</v>
+        <v>18.1532988</v>
       </c>
       <c r="N95">
-        <v>-12.29711737551021</v>
+        <v>-12.49023757551021</v>
       </c>
       <c r="O95">
-        <v>-2.533206179355104</v>
+        <v>-2.572988940555102</v>
       </c>
       <c r="P95">
-        <v>-9.763911196155107</v>
+        <v>-9.917248634955103</v>
       </c>
       <c r="Q95">
-        <v>-6.773911196155106</v>
+        <v>-6.927248634955102</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7809711005326179</v>
+        <v>0.9034996172880544</v>
       </c>
       <c r="T95">
-        <v>16.9785473564115</v>
+        <v>19.80830524914676</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06495428794037147</v>
+        <v>0.06426328487717604</v>
       </c>
       <c r="W95">
-        <v>0.2204837789036604</v>
+        <v>0.2206467174259619</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.315312077380444</v>
+        <v>0.3119576935785244</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9364,22 +9364,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2616178914176874</v>
+        <v>0.2635178914176874</v>
       </c>
       <c r="C96">
-        <v>-55.54217908449709</v>
+        <v>-56.52737240698357</v>
       </c>
       <c r="D96">
-        <v>19.04382091550291</v>
+        <v>18.87762759301643</v>
       </c>
       <c r="E96">
-        <v>57.886</v>
+        <v>58.70500000000001</v>
       </c>
       <c r="F96">
-        <v>76.986</v>
+        <v>77.80500000000001</v>
       </c>
       <c r="G96">
         <v>2.4</v>
@@ -9400,37 +9400,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M96">
-        <v>18.1532988</v>
+        <v>18.346419</v>
       </c>
       <c r="N96">
-        <v>-12.49023757551021</v>
+        <v>-12.6833577755102</v>
       </c>
       <c r="O96">
-        <v>-2.572988940555102</v>
+        <v>-2.612771701755102</v>
       </c>
       <c r="P96">
-        <v>-9.917248634955103</v>
+        <v>-10.0705860737551</v>
       </c>
       <c r="Q96">
-        <v>-6.927248634955102</v>
+        <v>-7.080586073755102</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9034996172880544</v>
+        <v>1.075039540745666</v>
       </c>
       <c r="T96">
-        <v>19.80830524914676</v>
+        <v>23.76996629897612</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06426328487717604</v>
+        <v>0.06358682924688998</v>
       </c>
       <c r="W96">
-        <v>0.2206467174259619</v>
+        <v>0.2208062256635833</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3119576935785244</v>
+        <v>0.308673928382961</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9446,22 +9446,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2635178914176874</v>
+        <v>0.2654178914176874</v>
       </c>
       <c r="C97">
-        <v>-56.52737240698357</v>
+        <v>-57.50969012301845</v>
       </c>
       <c r="D97">
-        <v>18.87762759301643</v>
+        <v>18.71430987698156</v>
       </c>
       <c r="E97">
-        <v>58.70500000000001</v>
+        <v>59.52400000000001</v>
       </c>
       <c r="F97">
-        <v>77.80500000000001</v>
+        <v>78.62400000000001</v>
       </c>
       <c r="G97">
         <v>2.4</v>
@@ -9482,37 +9482,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M97">
-        <v>18.346419</v>
+        <v>18.5395392</v>
       </c>
       <c r="N97">
-        <v>-12.6833577755102</v>
+        <v>-12.87647797551021</v>
       </c>
       <c r="O97">
-        <v>-2.612771701755102</v>
+        <v>-2.652554462955103</v>
       </c>
       <c r="P97">
-        <v>-10.0705860737551</v>
+        <v>-10.2239235125551</v>
       </c>
       <c r="Q97">
-        <v>-7.080586073755102</v>
+        <v>-7.233923512555103</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.075039540745666</v>
+        <v>1.332349425932083</v>
       </c>
       <c r="T97">
-        <v>23.76996629897612</v>
+        <v>29.71245787372016</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06358682924688998</v>
+        <v>0.06292446644223487</v>
       </c>
       <c r="W97">
-        <v>0.2208062256635833</v>
+        <v>0.220962410812921</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.308673928382961</v>
+        <v>0.3054585749623052</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9528,22 +9528,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2654178914176874</v>
+        <v>0.2673178914176874</v>
       </c>
       <c r="C98">
-        <v>-57.50969012301845</v>
+        <v>-58.48920622642979</v>
       </c>
       <c r="D98">
-        <v>18.71430987698156</v>
+        <v>18.55379377357021</v>
       </c>
       <c r="E98">
-        <v>59.52400000000001</v>
+        <v>60.343</v>
       </c>
       <c r="F98">
-        <v>78.62400000000001</v>
+        <v>79.443</v>
       </c>
       <c r="G98">
         <v>2.4</v>
@@ -9564,37 +9564,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M98">
-        <v>18.5395392</v>
+        <v>18.7326594</v>
       </c>
       <c r="N98">
-        <v>-12.87647797551021</v>
+        <v>-13.0695981755102</v>
       </c>
       <c r="O98">
-        <v>-2.652554462955103</v>
+        <v>-2.692337224155102</v>
       </c>
       <c r="P98">
-        <v>-10.2239235125551</v>
+        <v>-10.3772609513551</v>
       </c>
       <c r="Q98">
-        <v>-7.233923512555103</v>
+        <v>-7.387260951355101</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.332349425932079</v>
+        <v>1.761199234576106</v>
       </c>
       <c r="T98">
-        <v>29.71245787372008</v>
+        <v>39.61661049829344</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06292446644223487</v>
+        <v>0.06227576060262422</v>
       </c>
       <c r="W98">
-        <v>0.220962410812921</v>
+        <v>0.2211153756499012</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3054585749623052</v>
+        <v>0.302309517488467</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9610,22 +9610,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2673178914176874</v>
+        <v>0.2692178914176874</v>
       </c>
       <c r="C99">
-        <v>-58.48920622642979</v>
+        <v>-59.46599219399975</v>
       </c>
       <c r="D99">
-        <v>18.55379377357021</v>
+        <v>18.39600780600025</v>
       </c>
       <c r="E99">
-        <v>60.343</v>
+        <v>61.162</v>
       </c>
       <c r="F99">
-        <v>79.443</v>
+        <v>80.262</v>
       </c>
       <c r="G99">
         <v>2.4</v>
@@ -9646,37 +9646,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M99">
-        <v>18.7326594</v>
+        <v>18.9257796</v>
       </c>
       <c r="N99">
-        <v>-13.0695981755102</v>
+        <v>-13.26271837551021</v>
       </c>
       <c r="O99">
-        <v>-2.692337224155102</v>
+        <v>-2.732119985355102</v>
       </c>
       <c r="P99">
-        <v>-10.3772609513551</v>
+        <v>-10.5305983901551</v>
       </c>
       <c r="Q99">
-        <v>-7.387260951355101</v>
+        <v>-7.540598390155102</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.761199234576106</v>
+        <v>2.618898851864158</v>
       </c>
       <c r="T99">
-        <v>39.61661049829344</v>
+        <v>59.42491574744016</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06227576060262422</v>
+        <v>0.06164029365769948</v>
       </c>
       <c r="W99">
-        <v>0.2211153756499012</v>
+        <v>0.2212652187555145</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.302309517488467</v>
+        <v>0.2992247264936867</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9692,22 +9692,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2692178914176874</v>
+        <v>0.2711178914176874</v>
       </c>
       <c r="C100">
-        <v>-59.46599219399975</v>
+        <v>-60.44011709158993</v>
       </c>
       <c r="D100">
-        <v>18.39600780600025</v>
+        <v>18.24088290841008</v>
       </c>
       <c r="E100">
-        <v>61.162</v>
+        <v>61.981</v>
       </c>
       <c r="F100">
-        <v>80.262</v>
+        <v>81.081</v>
       </c>
       <c r="G100">
         <v>2.4</v>
@@ -9728,37 +9728,37 @@
         <v>5.663061224489796</v>
       </c>
       <c r="M100">
-        <v>18.9257796</v>
+        <v>19.1188998</v>
       </c>
       <c r="N100">
-        <v>-13.26271837551021</v>
+        <v>-13.4558385755102</v>
       </c>
       <c r="O100">
-        <v>-2.732119985355102</v>
+        <v>-2.771902746555102</v>
       </c>
       <c r="P100">
-        <v>-10.5305983901551</v>
+        <v>-10.6839358289551</v>
       </c>
       <c r="Q100">
-        <v>-7.540598390155102</v>
+        <v>-7.693935828955102</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.618898851864158</v>
+        <v>5.191997703728317</v>
       </c>
       <c r="T100">
-        <v>59.42491574744016</v>
+        <v>118.8498314948803</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06164029365769948</v>
+        <v>0.06101766442883382</v>
       </c>
       <c r="W100">
-        <v>0.2212652187555145</v>
+        <v>0.221412034727681</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9766,91 +9766,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2992247264936867</v>
+        <v>0.296202254508902</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2711178914176874</v>
-      </c>
-      <c r="C101">
-        <v>-60.44011709158993</v>
-      </c>
-      <c r="D101">
-        <v>18.24088290841008</v>
-      </c>
-      <c r="E101">
-        <v>61.981</v>
-      </c>
-      <c r="F101">
-        <v>81.081</v>
-      </c>
-      <c r="G101">
-        <v>2.4</v>
-      </c>
-      <c r="H101">
-        <v>62.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.653061224489797</v>
-      </c>
-      <c r="K101">
-        <v>2.99</v>
-      </c>
-      <c r="L101">
-        <v>5.663061224489796</v>
-      </c>
-      <c r="M101">
-        <v>19.1188998</v>
-      </c>
-      <c r="N101">
-        <v>-13.4558385755102</v>
-      </c>
-      <c r="O101">
-        <v>-2.771902746555102</v>
-      </c>
-      <c r="P101">
-        <v>-10.6839358289551</v>
-      </c>
-      <c r="Q101">
-        <v>-7.693935828955102</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.191997703728317</v>
-      </c>
-      <c r="T101">
-        <v>118.8498314948803</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06101766442883382</v>
-      </c>
-      <c r="W101">
-        <v>0.221412034727681</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.296202254508902</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
